--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4309,7 +4309,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4437,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 38.4, "op_wape_pct": 77.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 42.42, "rev_act": 120.4, "op_pred": -1.17, "op_act": -10.12}, {"q": "2025Q4", "rev_pred": 56.65, "rev_act": 71.77, "op_pred": -1.56, "op_act": -3.76}, {"q": "2026Q1", "rev_pred": 63.15, "rev_act": 104.01, "op_pred": -1.74, "op_act": -7.94}, {"q": "2026Q2", "rev_pred": 78.46, "rev_act": 94.65, "op_pred": -2.16, "op_act": -8.06}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 38.4, "op_wape_pct": 77.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 42.42, "rev_act": 120.4, "op_pred": -1.17, "op_act": -10.12}, {"q": "2025Q4", "rev_pred": 56.65, "rev_act": 71.77, "op_pred": -1.56, "op_act": -3.76}, {"q": "2026Q1", "rev_pred": 63.15, "rev_act": 104.01, "op_pred": -1.74, "op_act": -7.94}, {"q": "2026Q2", "rev_pred": 78.46, "rev_act": 94.65, "op_pred": -2.16, "op_act": -8.06}]}</t>
         </is>
       </c>
     </row>
@@ -10384,7 +10384,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -17736,7 +17736,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4545,7 +4545,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5416,35 +5416,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5535,35 +5535,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5654,35 +5654,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5773,35 +5773,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5892,35 +5892,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6011,35 +6011,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6130,35 +6130,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6249,35 +6249,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6657,7 +6657,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2495927601809955</v>
+        <v>0.2495927601809954</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02776052640237299</v>
+        <v>0.02776052640237282</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.1595244288940146</v>
+        <v>0.1595244288940148</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32932,7 +32932,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38449,7 +38449,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4545,7 +4545,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5416,35 +5416,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5535,35 +5535,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5654,35 +5654,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5773,35 +5773,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5892,35 +5892,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6011,35 +6011,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6130,35 +6130,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6249,35 +6249,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6384,7 +6384,7 @@
         <v>1443</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1518</v>
+        <v>1586</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6475,7 +6475,7 @@
         <v>2305</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>1572</v>
+        <v>1646</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -6657,7 +6657,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1512</v>
+        <v>1530.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9938,11 +9938,11 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>1518</v>
+        <v>1586</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,500원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,518원)</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32932,7 +32932,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38449,7 +38449,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40728,7 +40728,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4545,7 +4545,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18904,7 +18904,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -5416,35 +5416,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5535,35 +5535,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5654,35 +5654,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5773,35 +5773,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5892,35 +5892,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6011,35 +6011,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6130,35 +6130,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6249,35 +6249,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6384,7 +6384,7 @@
         <v>1443</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1586</v>
+        <v>1427</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6657,7 +6657,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1530.5</v>
+        <v>1509.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9938,7 +9938,7 @@
         </is>
       </c>
       <c r="D46" s="34" t="n">
-        <v>1586</v>
+        <v>1427</v>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="D47" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -32932,7 +32932,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38449,7 +38449,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40728,7 +40728,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,6 +167,7 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1678,136 +1679,76 @@
     <comment ref="AC41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AF41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AG41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AH41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AI41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — fin.shares.common_outstanding(2026Q2)</t>
-      </text>
-    </comment>
-    <comment ref="AC42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
       </text>
     </comment>
     <comment ref="AD42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AF42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AG42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AH42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AI42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AK42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AL42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AM42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AN42" authorId="0" shapeId="0">
-      <text>
-        <t>모델값 역산(implied): v / 전년동기 − 1
-= EPS(추정 구간은 일회성 미가정)</t>
-      </text>
-    </comment>
-    <comment ref="AD43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AI43" authorId="0" shapeId="0">
+    <comment ref="AI42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
       </text>
     </comment>
-    <comment ref="AN43" authorId="0" shapeId="0">
+    <comment ref="AN42" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
 직전 결산 DPS 0원 유지</t>
@@ -2185,121 +2126,121 @@
     </comment>
     <comment ref="AC11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 29억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 29억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AD11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -1억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -1억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -24억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -24억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -52억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -52억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -79억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -79억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -110억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -109억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -135억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -134억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -164억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -163억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -193억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -190억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -225억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
+        <t>추정: 이자손익 + 외환손익 0 + 파생상품손익 0 + 기타금융손익 +0.00억(잔차 실측 1분기 &lt; 4 → 0) (항등식); 이자손익 = 이자발생자산 -222억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4; 환율 효과는 환관련손익 행 별도
 [identity]</t>
       </text>
     </comment>
     <comment ref="AC12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 29억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 29억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AD12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -1억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -1억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AF12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -24억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -24억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AG12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -52억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -52억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AH12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -79억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -79억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AI12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -110억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -109억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AK12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -135억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -134억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AL12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -164억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -163억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AM12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -193억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -190억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
     <comment ref="AN12" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자발생자산 -225억 × 2.78%(주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
+        <t>추정: 이자발생자산 -222억 × 0.86%(CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))) − 총차입금 187억 × 15.95%(주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)) (연율) ÷ 4
 [interest]</t>
       </text>
     </comment>
@@ -3390,156 +3331,156 @@
     </comment>
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="G33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="H33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="I33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="L33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 17,937,698주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="M33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 18,779,448주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="N33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 18,779,448주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="O33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 18,779,448주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Q33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 22,842,424주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="R33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 30,132,955주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="S33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 30,132,640주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="T33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 30,630,152주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="V33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,254,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="W33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,429,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="X33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,429,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="Y33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,429,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="AA33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 39,624,969주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="AB33" authorId="0" shapeId="0">
       <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 39,624,969주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="AC33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AD33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AF33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AG33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AH33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AI33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AK33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AL33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AM33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AN33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — fin.shares.common_outstanding(2026Q2)
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
 [qoq]</t>
       </text>
     </comment>
@@ -3603,159 +3544,69 @@
 [per_share]</t>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="G35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="H35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="I35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="J35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="L35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="M35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="N35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="O35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Q35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="R35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="S35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="T35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="V35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="W35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="X35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="Y35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
-    <comment ref="AA35" authorId="0" shapeId="0">
-      <text>
-        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — = EPS(일회성 의심 없음)</t>
-      </text>
-    </comment>
     <comment ref="AB35" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): 지배NI 25억 − (비영업손익 33억 − 12분기 기준선 -2억) × (1 − 0.2%, 분기 유효세율(법인세 0억 ÷ 세전 25억)) × 지배 비중 1.00(그 분기 지배NI/NI) = -10억 ÷ 유통주식수 — 일회성 여부·세효과는 주석 미확인(모델 추정); 보고 EPS 63.6원</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 36억 × (1 − 세율 0.2% [분기 유효세율(법인세 0억 ÷ 세전 25억)]) × 지배 비중 1.0000 [그 분기 지배NI/NI] = -10억 ÷ 유통주식수 · 초과 = 비영업손익 33억 − 12분기 기준선 -2억 · 보고 EPS 254원(EPS 행 불변) · 상수 35.56·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AD35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AF35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AG35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AH35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AI35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AK35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AL35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AM35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AN35" authorId="0" shapeId="0">
       <text>
         <t>추정: = EPS(추정 구간은 일회성 미가정)
-[yoy]</t>
+[identity]</t>
       </text>
     </comment>
     <comment ref="AC36" authorId="0" shapeId="0">
@@ -4529,7 +4380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="1" max="1"/>
@@ -4545,7 +4396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4434,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식</t>
+          <t>subQ      분기 서브모델(억원 = 백만원/100). 확정 행: =IFERROR(VLOOKUP($D행,BS연결,MATCH(E$1,BS연결H,0),0)/100,"")  추정 행: 변수 시트 가정 셀 참조 수식. 외환손익·파생상품손익은 BS 계정 합·차, 기타금융손익은 잔차, OPM·EPS·BPS·PER·PBR 은 파생 수식, 조정EPS 는 EPS 참조(일회성 의심 분기만 산식 셀)</t>
         </is>
       </c>
     </row>
@@ -4694,7 +4545,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>· 이자율 자산 2.78% / 부채 15.95% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0278, 0.1595] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "주석 이자수익 ÷ 평균 이자발생자산(2025Q1~2026Q1)", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)"}</t>
+          <t>· 이자율 자산 0.85% / 부채 15.95% — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4, 최소자승 역산(모델 assumptions [0.0086, 0.1595] 는 4자리 반올림이라 그대로 쓰면 ±1억 어긋남) · 출처: {"asset": "CF 이자수취 ÷ 평균 이자발생자산(2025Q3~2026Q2; 주석 이자수익 연율 2.8% 클립 — 주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la))", "debt": "주석 이자비용 ÷ 평균 총차입금(2025Q1~2026Q1)"}</t>
         </is>
       </c>
     </row>
@@ -4708,50 +4559,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2026Q2 보고 254→조정 -105원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>· 연결된 가정: 판관비율, 지배주주비중, 이자율 · 연결 안 된 가정(모델값·분기별 역산 그대로): 세율(MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>· 밸류에이션 — PER 밴드 10.0/15.0/20.0배(sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 2개 &lt; 4)) · COE 9.0% · 12M fwd EPS 가중 0.5(가정). 모델 산출값 구간이며 추천이 아니다</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
-        </is>
-      </c>
+      <c r="A30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/101000.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
+          <t>출처: DART 정기보고서(연결/별도 재무제표·주석), FnGuide 계정명 규약, ECB 환율(api.frankfurter.app), 종가 네이버 정규장(aikstockdata 금융위 확정종가 대조·출처표기·비영리), 척당 계약 공시(contracts.json), forecast_panel(신규수주 패널)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
+          <t>재현: cd argus/kship/tools &amp;&amp; python3 kship_model_xlsx.py --model assets/models/101000.json --verify   (모델 json 부터: kship_model.py --build --all --xlsx · xlsx 58사 일괄: kship_model_xlsx.py --all --verify)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.45 가 단일 검정 5% 임계 r 0.71 미달(n=8) (suppliers_mentions·시차 3·수준·창 8)): 전년동기 × (1+g) 추세 / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 33억(영업이익 -8억의 4배, 12분기 중위 4억·기준선 -2억) → 지배NI 25억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -26.2원(보고 63.6원; 초과 비영업손익 36억 × (1 − 세율 0.2%) × 지배 비중 1.00 = 36억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -2/+5/-3/+41(중위 +2억) → 추정 2026Q3 -7억(차 -9억, -581%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>검증(--verify): 추정 전 분기·실적 수식 셀을 자체 계산기로 재계산해 모델값과 대조(억원 ±0.05), 세율·OPM·환율 forward·이자율·신규수주 셀을 바꿔 종속 셀이 기대만큼 움직이는지 확인. Excel 실개봉은 미확인(LibreOffice/Excel 없음)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
+        <is>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.45 가 단일 검정 5% 임계 r 0.71 미달(n=8, n_eff=8) (suppliers_mentions·시차 3·수준·창 8)): 전년동기 × (1+g) 추세 / 분기말 후 병합: aik 상장주식수 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 → 최신 유통주식수 9,906,242(자기주식 16,979 × 1/4 차감) — 실적 분기 주식수·EPS·BPS·DPS 를 1/4 로 환산(IAS 33.64 비교표시·수정주가 이력과 정합), 추정 분기·PER/PBR now·EV 는 최신 주식수. 효력일·단수주 처리는 정기보고서 캐시 밖(주요사항보고서 미수집) / 주식수 사건 환산: 2023Q1 1/4 병합(eps_reported 교차검증 confirmed) → 사건 전 실적 19분기의 주식수·EPS·BPS·DPS 를 비율 환산(IAS 33.64; 셀 kind estimate, basis 에 원주식수·비율) / 이자발생자산 이자율: 주석 연율 2.8% 이상(주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la)) → CF 연율 0.9% 로 클립(assumptions.interest_rate_check) / 총차입금 이자율: 주석 연율 16.0% 이상(주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 2.75배 · CF 창 2022Q4~2024Q1(la −9분기) 가 주석 창(~2026Q1)보다 오래됨 → CF 로 교체 안 함) — 더 오래된 CF 연율 5.8% 로 바꾸지 않고 주석 유지(assumptions.interest_rate_check) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 33억(영업이익 -8억의 4배, 12분기 중위 4억·기준선 -2억) → 지배NI 25억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -104.7원(보고 254.2원; 초과 비영업손익 36억 × (1 − 세율 0.2%) × 지배 비중 1.00 = 36억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -2/+5/-3/+41(중위 +2억) → 추정 2026Q3 -7억(차 -9억, -590%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 38.4, "op_wape_pct": 77.8, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "decision": "rejected", "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 42.42, "rev_act": 120.4, "op_pred": -1.17, "op_act": -10.12}, {"q": "2025Q4", "rev_pred": 56.65, "rev_act": 71.77, "op_pred": -1.56, "op_act": -3.76}, {"q": "2026Q1", "rev_pred": 63.15, "rev_act": 104.01, "op_pred": -1.74, "op_act": -7.94}, {"q": "2026Q2", "rev_pred": 78.46, "rev_act": 94.65, "op_pred": -2.16, "op_act": -8.06}]}</t>
         </is>
@@ -4768,7 +4626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO61"/>
+  <dimension ref="A1:AO60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6955,11 +6813,11 @@
         <v/>
       </c>
       <c r="AC22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AD22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AE22" s="25">
@@ -6967,19 +6825,19 @@
         <v/>
       </c>
       <c r="AF22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AG22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AH22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AI22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AJ22" s="25">
@@ -6987,19 +6845,19 @@
         <v/>
       </c>
       <c r="AK22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AL22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AM22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AN22" s="26">
-        <f>$D$54</f>
+        <f>$D$53</f>
         <v/>
       </c>
       <c r="AO22" s="25">
@@ -8205,11 +8063,11 @@
         <v/>
       </c>
       <c r="AC30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AD30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AE30" s="25">
@@ -8217,19 +8075,19 @@
         <v/>
       </c>
       <c r="AF30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AG30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AH30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AI30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AJ30" s="25">
@@ -8237,19 +8095,19 @@
         <v/>
       </c>
       <c r="AK30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AL30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AM30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AN30" s="26">
-        <f>$D$55</f>
+        <f>$D$54</f>
         <v/>
       </c>
       <c r="AO30" s="25">
@@ -8615,36 +8473,36 @@
         <v/>
       </c>
       <c r="AC33" s="30" t="n">
-        <v>0.004671692</v>
+        <v>0.006926205</v>
       </c>
       <c r="AD33" s="30" t="n">
-        <v>0.009824975999999999</v>
+        <v>0.002789916</v>
       </c>
       <c r="AE33" s="31" t="n"/>
       <c r="AF33" s="30" t="n">
-        <v>0.005343898</v>
+        <v>0.012269244</v>
       </c>
       <c r="AG33" s="30" t="n">
-        <v>0.00289408</v>
+        <v>0.003367536</v>
       </c>
       <c r="AH33" s="30" t="n">
-        <v>0.006898501</v>
+        <v>0.006747604</v>
       </c>
       <c r="AI33" s="30" t="n">
-        <v>0.001268665</v>
+        <v>0.001298913</v>
       </c>
       <c r="AJ33" s="31" t="n"/>
       <c r="AK33" s="30" t="n">
-        <v>0.00748775</v>
+        <v>0.009029466</v>
       </c>
       <c r="AL33" s="30" t="n">
-        <v>-0.006274586</v>
+        <v>-0.002196851</v>
       </c>
       <c r="AM33" s="30" t="n">
-        <v>0.006903262</v>
+        <v>0.009029348</v>
       </c>
       <c r="AN33" s="30" t="n">
-        <v>0.002181848</v>
+        <v>0.001938567</v>
       </c>
       <c r="AO33" s="31" t="n"/>
     </row>
@@ -8743,36 +8601,36 @@
         <v/>
       </c>
       <c r="AC34" s="30" t="n">
-        <v>0.004671692</v>
+        <v>0.006926205</v>
       </c>
       <c r="AD34" s="30" t="n">
-        <v>0.009824975999999999</v>
+        <v>0.002789916</v>
       </c>
       <c r="AE34" s="31" t="n"/>
       <c r="AF34" s="30" t="n">
-        <v>0.005343898</v>
+        <v>0.012269244</v>
       </c>
       <c r="AG34" s="30" t="n">
-        <v>0.00289408</v>
+        <v>0.003367536</v>
       </c>
       <c r="AH34" s="30" t="n">
-        <v>0.006898501</v>
+        <v>0.006747604</v>
       </c>
       <c r="AI34" s="30" t="n">
-        <v>0.001268665</v>
+        <v>0.001298913</v>
       </c>
       <c r="AJ34" s="31" t="n"/>
       <c r="AK34" s="30" t="n">
-        <v>0.00748775</v>
+        <v>0.009029466</v>
       </c>
       <c r="AL34" s="30" t="n">
-        <v>-0.006274586</v>
+        <v>-0.002196851</v>
       </c>
       <c r="AM34" s="30" t="n">
-        <v>0.006903262</v>
+        <v>0.009029348</v>
       </c>
       <c r="AN34" s="30" t="n">
-        <v>0.002181848</v>
+        <v>0.001938567</v>
       </c>
       <c r="AO34" s="31" t="n"/>
     </row>
@@ -8999,36 +8857,36 @@
         <v/>
       </c>
       <c r="AC36" s="24" t="n">
-        <v>0.163714041</v>
+        <v>0.164439479</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.113599309</v>
+        <v>0.11357646</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.119407484</v>
+        <v>0.118819125</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.103092784</v>
+        <v>0.10212324</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.108348445</v>
+        <v>0.107109203</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.07881571900000001</v>
+        <v>0.077296513</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.08559846</v>
+        <v>0.083981975</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.076189453</v>
+        <v>0.074398013</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.080855738</v>
+        <v>0.079045226</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.060395399</v>
+        <v>0.058375635</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -9127,36 +8985,36 @@
         <v/>
       </c>
       <c r="AC37" s="24" t="n">
-        <v>-1.021950684</v>
+        <v>-1.026828614</v>
       </c>
       <c r="AD37" s="24" t="n">
-        <v>37.619047619</v>
+        <v>30.766233766</v>
       </c>
       <c r="AE37" s="25" t="n"/>
       <c r="AF37" s="24" t="n">
-        <v>1.139745171</v>
+        <v>1.129190515</v>
       </c>
       <c r="AG37" s="24" t="n">
-        <v>0.514790626</v>
+        <v>0.5097926270000001</v>
       </c>
       <c r="AH37" s="24" t="n">
-        <v>0.393989348</v>
+        <v>0.390309042</v>
       </c>
       <c r="AI37" s="24" t="n">
-        <v>0.227781315</v>
+        <v>0.224204171</v>
       </c>
       <c r="AJ37" s="25" t="n"/>
       <c r="AK37" s="24" t="n">
-        <v>0.217529821</v>
+        <v>0.214525891</v>
       </c>
       <c r="AL37" s="24" t="n">
-        <v>0.172579566</v>
+        <v>0.169558263</v>
       </c>
       <c r="AM37" s="24" t="n">
-        <v>0.168041933</v>
+        <v>0.165491846</v>
       </c>
       <c r="AN37" s="24" t="n">
-        <v>0.116230506</v>
+        <v>0.113152194</v>
       </c>
       <c r="AO37" s="25" t="n"/>
     </row>
@@ -9581,7 +9439,7 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>0</v>
+        <v>-2.5e-08</v>
       </c>
       <c r="AD41" s="24" t="n">
         <v>0</v>
@@ -9617,264 +9475,176 @@
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>drv:조정EPS</t>
+          <t>drv:DPS</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>yoy</t>
+          <t>abs</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>조정EPS YoY</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="22" t="n"/>
-      <c r="G42" s="21" t="n"/>
-      <c r="H42" s="21" t="n"/>
-      <c r="I42" s="21" t="n"/>
-      <c r="J42" s="21">
-        <f>IFERROR(subQ!J35/subQ!E35-1,"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="22" t="n"/>
-      <c r="L42" s="21">
-        <f>IFERROR(subQ!L35/subQ!G35-1,"")</f>
-        <v/>
-      </c>
-      <c r="M42" s="21">
-        <f>IFERROR(subQ!M35/subQ!H35-1,"")</f>
-        <v/>
-      </c>
-      <c r="N42" s="21">
-        <f>IFERROR(subQ!N35/subQ!I35-1,"")</f>
-        <v/>
-      </c>
-      <c r="O42" s="21">
-        <f>IFERROR(subQ!O35/subQ!J35-1,"")</f>
-        <v/>
-      </c>
-      <c r="P42" s="22" t="n"/>
-      <c r="Q42" s="21">
-        <f>IFERROR(subQ!Q35/subQ!L35-1,"")</f>
-        <v/>
-      </c>
-      <c r="R42" s="21">
-        <f>IFERROR(subQ!R35/subQ!M35-1,"")</f>
-        <v/>
-      </c>
-      <c r="S42" s="21">
-        <f>IFERROR(subQ!S35/subQ!N35-1,"")</f>
-        <v/>
-      </c>
-      <c r="T42" s="21">
-        <f>IFERROR(subQ!T35/subQ!O35-1,"")</f>
-        <v/>
-      </c>
-      <c r="U42" s="22" t="n"/>
-      <c r="V42" s="21">
-        <f>IFERROR(subQ!V35/subQ!Q35-1,"")</f>
-        <v/>
-      </c>
-      <c r="W42" s="21">
-        <f>IFERROR(subQ!W35/subQ!R35-1,"")</f>
-        <v/>
-      </c>
-      <c r="X42" s="21">
-        <f>IFERROR(subQ!X35/subQ!S35-1,"")</f>
-        <v/>
-      </c>
-      <c r="Y42" s="21">
-        <f>IFERROR(subQ!Y35/subQ!T35-1,"")</f>
-        <v/>
-      </c>
-      <c r="Z42" s="22" t="n"/>
-      <c r="AA42" s="21">
-        <f>IFERROR(subQ!AA35/subQ!V35-1,"")</f>
-        <v/>
-      </c>
-      <c r="AB42" s="23">
-        <f>IFERROR(subQ!AB35/subQ!W35-1,"")</f>
-        <v/>
-      </c>
-      <c r="AC42" s="24" t="n">
-        <v>1.038567493</v>
-      </c>
-      <c r="AD42" s="24" t="n">
-        <v>-0.115384615</v>
-      </c>
-      <c r="AE42" s="25" t="n"/>
-      <c r="AF42" s="24" t="n">
-        <v>1.702702703</v>
-      </c>
-      <c r="AG42" s="24" t="n">
-        <v>1.580152672</v>
-      </c>
-      <c r="AH42" s="24" t="n">
-        <v>0.059459459</v>
-      </c>
-      <c r="AI42" s="24" t="n">
-        <v>0.056856187</v>
-      </c>
-      <c r="AJ42" s="25" t="n"/>
-      <c r="AK42" s="24" t="n">
-        <v>0.058571429</v>
-      </c>
-      <c r="AL42" s="24" t="n">
-        <v>0.059171598</v>
-      </c>
-      <c r="AM42" s="24" t="n">
-        <v>0.042091837</v>
-      </c>
-      <c r="AN42" s="24" t="n">
-        <v>0.044303797</v>
-      </c>
-      <c r="AO42" s="25" t="n"/>
+          <t>DPS (가정, 원)</t>
+        </is>
+      </c>
+      <c r="E42" s="27">
+        <f>subQ!E37</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>subQ!F37</f>
+        <v/>
+      </c>
+      <c r="G42" s="27">
+        <f>subQ!G37</f>
+        <v/>
+      </c>
+      <c r="H42" s="27">
+        <f>subQ!H37</f>
+        <v/>
+      </c>
+      <c r="I42" s="27">
+        <f>subQ!I37</f>
+        <v/>
+      </c>
+      <c r="J42" s="27">
+        <f>subQ!J37</f>
+        <v/>
+      </c>
+      <c r="K42" s="28">
+        <f>subQ!K37</f>
+        <v/>
+      </c>
+      <c r="L42" s="27">
+        <f>subQ!L37</f>
+        <v/>
+      </c>
+      <c r="M42" s="27">
+        <f>subQ!M37</f>
+        <v/>
+      </c>
+      <c r="N42" s="27">
+        <f>subQ!N37</f>
+        <v/>
+      </c>
+      <c r="O42" s="27">
+        <f>subQ!O37</f>
+        <v/>
+      </c>
+      <c r="P42" s="28">
+        <f>subQ!P37</f>
+        <v/>
+      </c>
+      <c r="Q42" s="27">
+        <f>subQ!Q37</f>
+        <v/>
+      </c>
+      <c r="R42" s="27">
+        <f>subQ!R37</f>
+        <v/>
+      </c>
+      <c r="S42" s="27">
+        <f>subQ!S37</f>
+        <v/>
+      </c>
+      <c r="T42" s="27">
+        <f>subQ!T37</f>
+        <v/>
+      </c>
+      <c r="U42" s="28">
+        <f>subQ!U37</f>
+        <v/>
+      </c>
+      <c r="V42" s="27">
+        <f>subQ!V37</f>
+        <v/>
+      </c>
+      <c r="W42" s="27">
+        <f>subQ!W37</f>
+        <v/>
+      </c>
+      <c r="X42" s="27">
+        <f>subQ!X37</f>
+        <v/>
+      </c>
+      <c r="Y42" s="27">
+        <f>subQ!Y37</f>
+        <v/>
+      </c>
+      <c r="Z42" s="28">
+        <f>subQ!Z37</f>
+        <v/>
+      </c>
+      <c r="AA42" s="27">
+        <f>subQ!AA37</f>
+        <v/>
+      </c>
+      <c r="AB42" s="29">
+        <f>subQ!AB37</f>
+        <v/>
+      </c>
+      <c r="AC42" s="32" t="n"/>
+      <c r="AD42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="31">
+        <f>subQ!AE37</f>
+        <v/>
+      </c>
+      <c r="AF42" s="32" t="n"/>
+      <c r="AG42" s="32" t="n"/>
+      <c r="AH42" s="32" t="n"/>
+      <c r="AI42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="31">
+        <f>subQ!AJ37</f>
+        <v/>
+      </c>
+      <c r="AK42" s="32" t="n"/>
+      <c r="AL42" s="32" t="n"/>
+      <c r="AM42" s="32" t="n"/>
+      <c r="AN42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="31">
+        <f>subQ!AO37</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>drv:DPS</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>abs</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>DPS (가정, 원)</t>
-        </is>
-      </c>
-      <c r="E43" s="27">
-        <f>subQ!E37</f>
-        <v/>
-      </c>
-      <c r="F43" s="28">
-        <f>subQ!F37</f>
-        <v/>
-      </c>
-      <c r="G43" s="27">
-        <f>subQ!G37</f>
-        <v/>
-      </c>
-      <c r="H43" s="27">
-        <f>subQ!H37</f>
-        <v/>
-      </c>
-      <c r="I43" s="27">
-        <f>subQ!I37</f>
-        <v/>
-      </c>
-      <c r="J43" s="27">
-        <f>subQ!J37</f>
-        <v/>
-      </c>
-      <c r="K43" s="28">
-        <f>subQ!K37</f>
-        <v/>
-      </c>
-      <c r="L43" s="27">
-        <f>subQ!L37</f>
-        <v/>
-      </c>
-      <c r="M43" s="27">
-        <f>subQ!M37</f>
-        <v/>
-      </c>
-      <c r="N43" s="27">
-        <f>subQ!N37</f>
-        <v/>
-      </c>
-      <c r="O43" s="27">
-        <f>subQ!O37</f>
-        <v/>
-      </c>
-      <c r="P43" s="28">
-        <f>subQ!P37</f>
-        <v/>
-      </c>
-      <c r="Q43" s="27">
-        <f>subQ!Q37</f>
-        <v/>
-      </c>
-      <c r="R43" s="27">
-        <f>subQ!R37</f>
-        <v/>
-      </c>
-      <c r="S43" s="27">
-        <f>subQ!S37</f>
-        <v/>
-      </c>
-      <c r="T43" s="27">
-        <f>subQ!T37</f>
-        <v/>
-      </c>
-      <c r="U43" s="28">
-        <f>subQ!U37</f>
-        <v/>
-      </c>
-      <c r="V43" s="27">
-        <f>subQ!V37</f>
-        <v/>
-      </c>
-      <c r="W43" s="27">
-        <f>subQ!W37</f>
-        <v/>
-      </c>
-      <c r="X43" s="27">
-        <f>subQ!X37</f>
-        <v/>
-      </c>
-      <c r="Y43" s="27">
-        <f>subQ!Y37</f>
-        <v/>
-      </c>
-      <c r="Z43" s="28">
-        <f>subQ!Z37</f>
-        <v/>
-      </c>
-      <c r="AA43" s="27">
-        <f>subQ!AA37</f>
-        <v/>
-      </c>
-      <c r="AB43" s="29">
-        <f>subQ!AB37</f>
-        <v/>
-      </c>
-      <c r="AC43" s="32" t="n"/>
-      <c r="AD43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="31">
-        <f>subQ!AE37</f>
-        <v/>
-      </c>
-      <c r="AF43" s="32" t="n"/>
-      <c r="AG43" s="32" t="n"/>
-      <c r="AH43" s="32" t="n"/>
-      <c r="AI43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="31">
-        <f>subQ!AJ37</f>
-        <v/>
-      </c>
-      <c r="AK43" s="32" t="n"/>
-      <c r="AL43" s="32" t="n"/>
-      <c r="AM43" s="32" t="n"/>
-      <c r="AN43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="31">
-        <f>subQ!AO37</f>
-        <v/>
-      </c>
+      <c r="F43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+      <c r="P43" s="9" t="n"/>
+      <c r="U43" s="9" t="n"/>
+      <c r="Z43" s="9" t="n"/>
+      <c r="AB43" s="5" t="n"/>
+      <c r="AC43" s="10" t="n"/>
+      <c r="AD43" s="10" t="n"/>
+      <c r="AE43" s="11" t="n"/>
+      <c r="AF43" s="10" t="n"/>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="11" t="n"/>
+      <c r="AK43" s="10" t="n"/>
+      <c r="AL43" s="10" t="n"/>
+      <c r="AM43" s="10" t="n"/>
+      <c r="AN43" s="10" t="n"/>
+      <c r="AO43" s="11" t="n"/>
     </row>
     <row r="44">
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>3. 밸류에이션·스칼라</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+        </is>
+      </c>
       <c r="F44" s="9" t="n"/>
       <c r="K44" s="9" t="n"/>
       <c r="P44" s="9" t="n"/>
@@ -9896,14 +9666,22 @@
       <c r="AO44" s="11" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>3. 밸류에이션·스칼라</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>노란 셀 = 가정. '연결' 표시는 추정 전 분기 수식이 이 셀을 참조한다는 뜻</t>
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>sc:종가</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>종가</t>
+        </is>
+      </c>
+      <c r="D45" s="34" t="n">
+        <v>1427</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,518원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9929,20 +9707,22 @@
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>sc:종가</t>
+          <t>sc:기준일</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>종가</t>
-        </is>
-      </c>
-      <c r="D46" s="34" t="n">
-        <v>1427</v>
+          <t>기준일</t>
+        </is>
+      </c>
+      <c r="D46" s="35" t="inlineStr">
+        <is>
+          <t>20261008</t>
+        </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,518원)</t>
+          <t>종가 기준일</t>
         </is>
       </c>
       <c r="F46" s="9" t="n"/>
@@ -9968,22 +9748,20 @@
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>sc:기준일</t>
+          <t>sc:COE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>기준일</t>
-        </is>
-      </c>
-      <c r="D47" s="35" t="inlineStr">
-        <is>
-          <t>20261008</t>
-        </is>
+          <t>COE</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="n">
+        <v>0.09</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>종가 기준일</t>
+          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10009,20 +9787,20 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>sc:COE</t>
+          <t>sc:PER_lo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>COE</t>
-        </is>
-      </c>
-      <c r="D48" s="24" t="n">
-        <v>0.09</v>
+          <t>PER_lo</t>
+        </is>
+      </c>
+      <c r="D48" s="30" t="n">
+        <v>10</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>자기자본비용(가정) — TP 적정 PBR = ROE/COE</t>
+          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 2개 &lt; 4)</t>
         </is>
       </c>
       <c r="F48" s="9" t="n"/>
@@ -10048,20 +9826,20 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_lo</t>
+          <t>sc:PER_mid</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PER_lo</t>
+          <t>PER_mid</t>
         </is>
       </c>
       <c r="D49" s="30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 하단(배) — sector_default(레퍼런스 TP_PE PB 예시 10/15/20배; 과거 양(+)EPS 분기 2개 &lt; 4)</t>
+          <t>PER 밴드 중단(배)</t>
         </is>
       </c>
       <c r="F49" s="9" t="n"/>
@@ -10087,20 +9865,20 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_mid</t>
+          <t>sc:PER_hi</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PER_mid</t>
+          <t>PER_hi</t>
         </is>
       </c>
       <c r="D50" s="30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 중단(배)</t>
+          <t>PER 밴드 상단(배)</t>
         </is>
       </c>
       <c r="F50" s="9" t="n"/>
@@ -10126,20 +9904,20 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>sc:PER_hi</t>
+          <t>sc:EPS_Y1가중</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>PER_hi</t>
-        </is>
-      </c>
-      <c r="D51" s="30" t="n">
-        <v>20</v>
+          <t>EPS_Y1가중</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="n">
+        <v>0.5</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>PER 밴드 상단(배)</t>
+          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
         </is>
       </c>
       <c r="F51" s="9" t="n"/>
@@ -10165,20 +9943,20 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>sc:EPS_Y1가중</t>
+          <t>sc:세율</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EPS_Y1가중</t>
-        </is>
-      </c>
-      <c r="D52" s="24" t="n">
-        <v>0.5</v>
+          <t>세율</t>
+        </is>
+      </c>
+      <c r="D52" s="36" t="n">
+        <v>0.22</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>12M fwd EPS = FY(last_actual연도)E × w + FY+1E × (1−w) — 기준 분기 2Q 이면 0.5(가정)</t>
+          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 0.2% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
         </is>
       </c>
       <c r="F52" s="9" t="n"/>
@@ -10204,20 +9982,20 @@
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>sc:세율</t>
+          <t>sc:판관비율</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>세율</t>
+          <t>판관비율</t>
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.22</v>
+        <v>0.2495927601809955</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>참고(연결 안 됨: MAX(세전,0)×단일 세율로 재현 불가(지주 자회사 합산 등) → 분기별 역산) — 모델 assumptions 값 · 최근 12분기 세전 합 ≤ 0; 세전 &gt; 0 분기 중위 0.2% 도 5~27% 밖 → 법정세율 근사 22% 가정</t>
+          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.2496)</t>
         </is>
       </c>
       <c r="F53" s="9" t="n"/>
@@ -10243,20 +10021,20 @@
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>sc:판관비율</t>
+          <t>sc:지배주주비중</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>판관비율</t>
+          <t>지배주주비중</t>
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.2495927601809954</v>
+        <v>1</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>연결 — 판관비 = 매출액 × 판관비율(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.2496)</t>
+          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
         </is>
       </c>
       <c r="F54" s="9" t="n"/>
@@ -10282,20 +10060,20 @@
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>sc:지배주주비중</t>
+          <t>sc:이자율_자산</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>지배주주비중</t>
+          <t>이자율_자산</t>
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>1</v>
+        <v>0.008530302041496976</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>연결 — 지배주주순이익 = 당기순이익 × 비중(역산, 재현 오차 ≤ 0.05억)</t>
+          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0086)</t>
         </is>
       </c>
       <c r="F55" s="9" t="n"/>
@@ -10321,20 +10099,20 @@
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_자산</t>
+          <t>sc:이자율_부채</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>이자율_자산</t>
+          <t>이자율_부채</t>
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.02776052640237282</v>
+        <v>0.1595193996304005</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>연결 — 이자손익 = (전분기 이자발생자산 × 자산이자율 − 전분기 총차입금 × 부채이자율)/4(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.0278)</t>
+          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1595)</t>
         </is>
       </c>
       <c r="F56" s="9" t="n"/>
@@ -10360,20 +10138,18 @@
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>sc:이자율_부채</t>
+          <t>sc:배당성향</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>이자율_부채</t>
-        </is>
-      </c>
-      <c r="D57" s="36" t="n">
-        <v>0.1595244288940148</v>
-      </c>
+          <t>배당성향</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>연결 — 같은 수식의 부채 쪽(총차입금 행이 없으면 0)(역산, 재현 오차 ≤ 0.05억 · 모델 assumptions 0.1595)</t>
+          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
         </is>
       </c>
       <c r="F57" s="9" t="n"/>
@@ -10399,18 +10175,18 @@
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>sc:배당성향</t>
+          <t>sc:외화순노출_백만$</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>배당성향</t>
-        </is>
-      </c>
-      <c r="D58" s="24" t="n"/>
+          <t>외화순노출_백만$</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="n"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>배당성향(참고 — 모델은 직전 DPS 유지·Q2 지급 가정)</t>
+          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
         </is>
       </c>
       <c r="F58" s="9" t="n"/>
@@ -10436,18 +10212,18 @@
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>sc:외화순노출_백만$</t>
+          <t>sc:헤지비율</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>외화순노출_백만$</t>
-        </is>
-      </c>
-      <c r="D59" s="30" t="n"/>
+          <t>헤지비율</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="n"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>외화 순노출 × Δ기말환율 (외화 시트 방식) — 외화 순노출 미공시(face) → 0 + 표기</t>
+          <t>sls 없음</t>
         </is>
       </c>
       <c r="F59" s="9" t="n"/>
@@ -10473,15 +10249,15 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>sc:헤지비율</t>
+          <t>sc:헤지환율_약정</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>헤지비율</t>
-        </is>
-      </c>
-      <c r="D60" s="24" t="n"/>
+          <t>헤지환율_약정</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="n"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
           <t>sls 없음</t>
@@ -10506,43 +10282,6 @@
       <c r="AM60" s="10" t="n"/>
       <c r="AN60" s="10" t="n"/>
       <c r="AO60" s="11" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="12" t="inlineStr">
-        <is>
-          <t>sc:헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>헤지환율_약정</t>
-        </is>
-      </c>
-      <c r="D61" s="16" t="n"/>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>sls 없음</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="n"/>
-      <c r="K61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="U61" s="9" t="n"/>
-      <c r="Z61" s="9" t="n"/>
-      <c r="AB61" s="5" t="n"/>
-      <c r="AC61" s="10" t="n"/>
-      <c r="AD61" s="10" t="n"/>
-      <c r="AE61" s="11" t="n"/>
-      <c r="AF61" s="10" t="n"/>
-      <c r="AG61" s="10" t="n"/>
-      <c r="AH61" s="10" t="n"/>
-      <c r="AI61" s="10" t="n"/>
-      <c r="AJ61" s="11" t="n"/>
-      <c r="AK61" s="10" t="n"/>
-      <c r="AL61" s="10" t="n"/>
-      <c r="AM61" s="10" t="n"/>
-      <c r="AN61" s="10" t="n"/>
-      <c r="AO61" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10804,7 +10543,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18904,7 +18643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19836,7 +19575,7 @@
         <v>5519.01</v>
       </c>
       <c r="X11" s="18" t="n">
-        <v>4818.4</v>
+        <v>4819.01</v>
       </c>
       <c r="Y11" s="18" t="n">
         <v>2876.81</v>
@@ -19931,7 +19670,7 @@
         <v>14342.8</v>
       </c>
       <c r="X12" s="18" t="n">
-        <v>13642.19</v>
+        <v>13642.8</v>
       </c>
       <c r="Y12" s="18" t="n">
         <v>11696.85</v>
@@ -22278,7 +22017,7 @@
         <v>10991.08</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>7116.53</v>
+        <v>7117.14</v>
       </c>
       <c r="Y38" s="18" t="n">
         <v>5333.17</v>
@@ -27829,11 +27568,11 @@
       </c>
       <c r="AB12" s="19" t="n"/>
       <c r="AC12" s="20">
-        <f>IFERROR((AB29*변수!$D$56-AB27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AB29*변수!$D$55-AB27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AD12" s="20">
-        <f>IFERROR((AC29*변수!$D$56-AC27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AC29*변수!$D$55-AC27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AE12" s="38">
@@ -27841,19 +27580,19 @@
         <v/>
       </c>
       <c r="AF12" s="20">
-        <f>IFERROR((AD29*변수!$D$56-AD27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AD29*변수!$D$55-AD27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AG12" s="20">
-        <f>IFERROR((AF29*변수!$D$56-AF27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AF29*변수!$D$55-AF27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AH12" s="20">
-        <f>IFERROR((AG29*변수!$D$56-AG27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AG29*변수!$D$55-AG27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AI12" s="20">
-        <f>IFERROR((AH29*변수!$D$56-AH27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AH29*변수!$D$55-AH27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AJ12" s="38">
@@ -27861,19 +27600,19 @@
         <v/>
       </c>
       <c r="AK12" s="20">
-        <f>IFERROR((AI29*변수!$D$56-AI27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AI29*변수!$D$55-AI27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AL12" s="20">
-        <f>IFERROR((AK29*변수!$D$56-AK27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AK29*변수!$D$55-AK27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AM12" s="20">
-        <f>IFERROR((AL29*변수!$D$56-AL27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AL29*변수!$D$55-AL27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AN12" s="20">
-        <f>IFERROR((AM29*변수!$D$56-AM27*변수!$D$57)/4,"")</f>
+        <f>IFERROR((AM29*변수!$D$55-AM27*변수!$D$56)/4,"")</f>
         <v/>
       </c>
       <c r="AO12" s="38">
@@ -30918,82 +30657,82 @@
           <t>유통주식수</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
-        <v>71.751</v>
+      <c r="E33" s="32" t="n">
+        <v>4.4844245</v>
       </c>
       <c r="F33" s="28">
         <f>E33</f>
         <v/>
       </c>
-      <c r="G33" s="27" t="n">
-        <v>71.751</v>
-      </c>
-      <c r="H33" s="27" t="n">
-        <v>71.751</v>
-      </c>
-      <c r="I33" s="27" t="n">
-        <v>71.751</v>
-      </c>
-      <c r="J33" s="27" t="n">
-        <v>71.751</v>
+      <c r="G33" s="32" t="n">
+        <v>4.4844245</v>
+      </c>
+      <c r="H33" s="32" t="n">
+        <v>4.4844245</v>
+      </c>
+      <c r="I33" s="32" t="n">
+        <v>4.4844245</v>
+      </c>
+      <c r="J33" s="32" t="n">
+        <v>4.4844245</v>
       </c>
       <c r="K33" s="28">
         <f>J33</f>
         <v/>
       </c>
-      <c r="L33" s="27" t="n">
-        <v>17.938</v>
-      </c>
-      <c r="M33" s="27" t="n">
-        <v>18.779</v>
-      </c>
-      <c r="N33" s="27" t="n">
-        <v>18.779</v>
-      </c>
-      <c r="O33" s="27" t="n">
-        <v>18.779</v>
+      <c r="L33" s="32" t="n">
+        <v>4.4844245</v>
+      </c>
+      <c r="M33" s="32" t="n">
+        <v>4.694862</v>
+      </c>
+      <c r="N33" s="32" t="n">
+        <v>4.694862</v>
+      </c>
+      <c r="O33" s="32" t="n">
+        <v>4.694862</v>
       </c>
       <c r="P33" s="28">
         <f>O33</f>
         <v/>
       </c>
-      <c r="Q33" s="27" t="n">
-        <v>22.842</v>
-      </c>
-      <c r="R33" s="27" t="n">
-        <v>30.133</v>
-      </c>
-      <c r="S33" s="27" t="n">
-        <v>30.133</v>
-      </c>
-      <c r="T33" s="27" t="n">
-        <v>30.63</v>
+      <c r="Q33" s="32" t="n">
+        <v>5.710606</v>
+      </c>
+      <c r="R33" s="32" t="n">
+        <v>7.53323875</v>
+      </c>
+      <c r="S33" s="32" t="n">
+        <v>7.53316</v>
+      </c>
+      <c r="T33" s="32" t="n">
+        <v>7.657538</v>
       </c>
       <c r="U33" s="28">
         <f>T33</f>
         <v/>
       </c>
-      <c r="V33" s="27" t="n">
-        <v>33.255</v>
-      </c>
-      <c r="W33" s="27" t="n">
-        <v>33.43</v>
-      </c>
-      <c r="X33" s="27" t="n">
-        <v>33.43</v>
-      </c>
-      <c r="Y33" s="27" t="n">
-        <v>33.43</v>
+      <c r="V33" s="32" t="n">
+        <v>8.31370575</v>
+      </c>
+      <c r="W33" s="32" t="n">
+        <v>8.35745575</v>
+      </c>
+      <c r="X33" s="32" t="n">
+        <v>8.35745575</v>
+      </c>
+      <c r="Y33" s="32" t="n">
+        <v>8.35745575</v>
       </c>
       <c r="Z33" s="28">
         <f>Y33</f>
         <v/>
       </c>
-      <c r="AA33" s="27" t="n">
-        <v>39.625</v>
-      </c>
-      <c r="AB33" s="29" t="n">
-        <v>39.625</v>
+      <c r="AA33" s="32" t="n">
+        <v>9.90624225</v>
+      </c>
+      <c r="AB33" s="39" t="n">
+        <v>9.90624225</v>
       </c>
       <c r="AC33" s="32">
         <f>IFERROR(AB33*(1+변수!AC41),"")</f>
@@ -31236,86 +30975,105 @@
           <t>조정 EPS(일회성 의심 분기의 초과 비영업손익 세후 차감 — 모델 추정)</t>
         </is>
       </c>
-      <c r="E35" s="18" t="n">
-        <v>-67.09999999999999</v>
+      <c r="E35" s="18">
+        <f>IFERROR(E34,"")</f>
+        <v/>
       </c>
       <c r="F35" s="37" t="n"/>
-      <c r="G35" s="18" t="n">
-        <v>-24.9</v>
-      </c>
-      <c r="H35" s="18" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="I35" s="18" t="n">
-        <v>-45.6</v>
-      </c>
-      <c r="J35" s="18" t="n">
-        <v>-115.2</v>
+      <c r="G35" s="18">
+        <f>IFERROR(G34,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="18">
+        <f>IFERROR(H34,"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="18">
+        <f>IFERROR(I34,"")</f>
+        <v/>
+      </c>
+      <c r="J35" s="18">
+        <f>IFERROR(J34,"")</f>
+        <v/>
       </c>
       <c r="K35" s="37">
         <f>SUM(G35:J35)</f>
         <v/>
       </c>
-      <c r="L35" s="18" t="n">
-        <v>-59.7</v>
-      </c>
-      <c r="M35" s="18" t="n">
-        <v>116.7</v>
-      </c>
-      <c r="N35" s="18" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="O35" s="18" t="n">
-        <v>107.2</v>
+      <c r="L35" s="18">
+        <f>IFERROR(L34,"")</f>
+        <v/>
+      </c>
+      <c r="M35" s="18">
+        <f>IFERROR(M34,"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="18">
+        <f>IFERROR(N34,"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="18">
+        <f>IFERROR(O34,"")</f>
+        <v/>
       </c>
       <c r="P35" s="37">
         <f>SUM(L35:O35)</f>
         <v/>
       </c>
-      <c r="Q35" s="18" t="n">
-        <v>-90.5</v>
-      </c>
-      <c r="R35" s="18" t="n">
-        <v>-121.8</v>
-      </c>
-      <c r="S35" s="18" t="n">
-        <v>39.3</v>
-      </c>
-      <c r="T35" s="18" t="n">
-        <v>-22.7</v>
+      <c r="Q35" s="18">
+        <f>IFERROR(Q34,"")</f>
+        <v/>
+      </c>
+      <c r="R35" s="18">
+        <f>IFERROR(R34,"")</f>
+        <v/>
+      </c>
+      <c r="S35" s="18">
+        <f>IFERROR(S34,"")</f>
+        <v/>
+      </c>
+      <c r="T35" s="18">
+        <f>IFERROR(T34,"")</f>
+        <v/>
       </c>
       <c r="U35" s="37">
         <f>SUM(Q35:T35)</f>
         <v/>
       </c>
-      <c r="V35" s="18" t="n">
-        <v>-58.5</v>
-      </c>
-      <c r="W35" s="18" t="n">
-        <v>-55</v>
-      </c>
-      <c r="X35" s="18" t="n">
-        <v>-36.3</v>
-      </c>
-      <c r="Y35" s="18" t="n">
-        <v>-67.59999999999999</v>
+      <c r="V35" s="18">
+        <f>IFERROR(V34,"")</f>
+        <v/>
+      </c>
+      <c r="W35" s="18">
+        <f>IFERROR(W34,"")</f>
+        <v/>
+      </c>
+      <c r="X35" s="18">
+        <f>IFERROR(X34,"")</f>
+        <v/>
+      </c>
+      <c r="Y35" s="18">
+        <f>IFERROR(Y34,"")</f>
+        <v/>
       </c>
       <c r="Z35" s="37">
         <f>SUM(V35:Y35)</f>
         <v/>
       </c>
-      <c r="AA35" s="18" t="n">
-        <v>-25.9</v>
-      </c>
-      <c r="AB35" s="39" t="n">
-        <v>-26.2</v>
+      <c r="AA35" s="18">
+        <f>IFERROR(AA34,"")</f>
+        <v/>
+      </c>
+      <c r="AB35" s="40">
+        <f>IFERROR((AB21-(35.56)*(1.0))*100/AB33,"")</f>
+        <v/>
       </c>
       <c r="AC35" s="20">
-        <f>IFERROR(X35*(1+변수!AC42),"")</f>
+        <f>IFERROR(AC34,"")</f>
         <v/>
       </c>
       <c r="AD35" s="20">
-        <f>IFERROR(Y35*(1+변수!AD42),"")</f>
+        <f>IFERROR(AD34,"")</f>
         <v/>
       </c>
       <c r="AE35" s="38">
@@ -31323,19 +31081,19 @@
         <v/>
       </c>
       <c r="AF35" s="20">
-        <f>IFERROR(AA35*(1+변수!AF42),"")</f>
+        <f>IFERROR(AF34,"")</f>
         <v/>
       </c>
       <c r="AG35" s="20">
-        <f>IFERROR(AB35*(1+변수!AG42),"")</f>
+        <f>IFERROR(AG34,"")</f>
         <v/>
       </c>
       <c r="AH35" s="20">
-        <f>IFERROR(AC35*(1+변수!AH42),"")</f>
+        <f>IFERROR(AH34,"")</f>
         <v/>
       </c>
       <c r="AI35" s="20">
-        <f>IFERROR(AD35*(1+변수!AI42),"")</f>
+        <f>IFERROR(AI34,"")</f>
         <v/>
       </c>
       <c r="AJ35" s="38">
@@ -31343,19 +31101,19 @@
         <v/>
       </c>
       <c r="AK35" s="20">
-        <f>IFERROR(AF35*(1+변수!AK42),"")</f>
+        <f>IFERROR(AK34,"")</f>
         <v/>
       </c>
       <c r="AL35" s="20">
-        <f>IFERROR(AG35*(1+변수!AL42),"")</f>
+        <f>IFERROR(AL34,"")</f>
         <v/>
       </c>
       <c r="AM35" s="20">
-        <f>IFERROR(AH35*(1+변수!AM42),"")</f>
+        <f>IFERROR(AM34,"")</f>
         <v/>
       </c>
       <c r="AN35" s="20">
-        <f>IFERROR(AI35*(1+변수!AN42),"")</f>
+        <f>IFERROR(AN34,"")</f>
         <v/>
       </c>
       <c r="AO35" s="38">
@@ -31604,7 +31362,7 @@
       <c r="AB37" s="19" t="n"/>
       <c r="AC37" s="20" t="n"/>
       <c r="AD37" s="20">
-        <f>변수!AD43</f>
+        <f>변수!AD42</f>
         <v/>
       </c>
       <c r="AE37" s="38">
@@ -31615,7 +31373,7 @@
       <c r="AG37" s="20" t="n"/>
       <c r="AH37" s="20" t="n"/>
       <c r="AI37" s="20">
-        <f>변수!AI43</f>
+        <f>변수!AI42</f>
         <v/>
       </c>
       <c r="AJ37" s="38">
@@ -31626,7 +31384,7 @@
       <c r="AL37" s="20" t="n"/>
       <c r="AM37" s="20" t="n"/>
       <c r="AN37" s="20">
-        <f>변수!AN43</f>
+        <f>변수!AN42</f>
         <v/>
       </c>
       <c r="AO37" s="38">
@@ -31700,25 +31458,25 @@
       </c>
       <c r="AA38" s="13" t="n"/>
       <c r="AB38" s="15" t="n"/>
-      <c r="AC38" s="40" t="n"/>
-      <c r="AD38" s="40" t="n"/>
-      <c r="AE38" s="41">
+      <c r="AC38" s="41" t="n"/>
+      <c r="AD38" s="41" t="n"/>
+      <c r="AE38" s="42">
         <f>AD38</f>
         <v/>
       </c>
-      <c r="AF38" s="40" t="n"/>
-      <c r="AG38" s="40" t="n"/>
-      <c r="AH38" s="40" t="n"/>
-      <c r="AI38" s="40" t="n"/>
-      <c r="AJ38" s="41">
+      <c r="AF38" s="41" t="n"/>
+      <c r="AG38" s="41" t="n"/>
+      <c r="AH38" s="41" t="n"/>
+      <c r="AI38" s="41" t="n"/>
+      <c r="AJ38" s="42">
         <f>AI38</f>
         <v/>
       </c>
-      <c r="AK38" s="40" t="n"/>
-      <c r="AL38" s="40" t="n"/>
-      <c r="AM38" s="40" t="n"/>
-      <c r="AN38" s="40" t="n"/>
-      <c r="AO38" s="41">
+      <c r="AK38" s="41" t="n"/>
+      <c r="AL38" s="41" t="n"/>
+      <c r="AM38" s="41" t="n"/>
+      <c r="AN38" s="41" t="n"/>
+      <c r="AO38" s="42">
         <f>AN38</f>
         <v/>
       </c>
@@ -31840,55 +31598,55 @@
         <f>IFERROR(변수!AB18/AB36,"")</f>
         <v/>
       </c>
-      <c r="AC39" s="40">
-        <f>IFERROR(변수!$D$46/AC36,"")</f>
-        <v/>
-      </c>
-      <c r="AD39" s="40">
-        <f>IFERROR(변수!$D$46/AD36,"")</f>
-        <v/>
-      </c>
-      <c r="AE39" s="41">
+      <c r="AC39" s="41">
+        <f>IFERROR(변수!$D$45/AC36,"")</f>
+        <v/>
+      </c>
+      <c r="AD39" s="41">
+        <f>IFERROR(변수!$D$45/AD36,"")</f>
+        <v/>
+      </c>
+      <c r="AE39" s="42">
         <f>AD39</f>
         <v/>
       </c>
-      <c r="AF39" s="40">
-        <f>IFERROR(변수!$D$46/AF36,"")</f>
-        <v/>
-      </c>
-      <c r="AG39" s="40">
-        <f>IFERROR(변수!$D$46/AG36,"")</f>
-        <v/>
-      </c>
-      <c r="AH39" s="40">
-        <f>IFERROR(변수!$D$46/AH36,"")</f>
-        <v/>
-      </c>
-      <c r="AI39" s="40">
-        <f>IFERROR(변수!$D$46/AI36,"")</f>
-        <v/>
-      </c>
-      <c r="AJ39" s="41">
+      <c r="AF39" s="41">
+        <f>IFERROR(변수!$D$45/AF36,"")</f>
+        <v/>
+      </c>
+      <c r="AG39" s="41">
+        <f>IFERROR(변수!$D$45/AG36,"")</f>
+        <v/>
+      </c>
+      <c r="AH39" s="41">
+        <f>IFERROR(변수!$D$45/AH36,"")</f>
+        <v/>
+      </c>
+      <c r="AI39" s="41">
+        <f>IFERROR(변수!$D$45/AI36,"")</f>
+        <v/>
+      </c>
+      <c r="AJ39" s="42">
         <f>AI39</f>
         <v/>
       </c>
-      <c r="AK39" s="40">
-        <f>IFERROR(변수!$D$46/AK36,"")</f>
-        <v/>
-      </c>
-      <c r="AL39" s="40">
-        <f>IFERROR(변수!$D$46/AL36,"")</f>
-        <v/>
-      </c>
-      <c r="AM39" s="40">
-        <f>IFERROR(변수!$D$46/AM36,"")</f>
-        <v/>
-      </c>
-      <c r="AN39" s="40">
-        <f>IFERROR(변수!$D$46/AN36,"")</f>
-        <v/>
-      </c>
-      <c r="AO39" s="41">
+      <c r="AK39" s="41">
+        <f>IFERROR(변수!$D$45/AK36,"")</f>
+        <v/>
+      </c>
+      <c r="AL39" s="41">
+        <f>IFERROR(변수!$D$45/AL36,"")</f>
+        <v/>
+      </c>
+      <c r="AM39" s="41">
+        <f>IFERROR(변수!$D$45/AM36,"")</f>
+        <v/>
+      </c>
+      <c r="AN39" s="41">
+        <f>IFERROR(변수!$D$45/AN36,"")</f>
+        <v/>
+      </c>
+      <c r="AO39" s="42">
         <f>AN39</f>
         <v/>
       </c>
@@ -32856,7 +32614,7 @@
           <t>1Q26</t>
         </is>
       </c>
-      <c r="W1" s="42" t="inlineStr">
+      <c r="W1" s="43" t="inlineStr">
         <is>
           <t>2Q26</t>
         </is>
@@ -32919,10 +32677,10 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D46</f>
-        <v/>
-      </c>
-      <c r="W2" s="43" t="n"/>
+        <f>변수!D45</f>
+        <v/>
+      </c>
+      <c r="W2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -32989,7 +32747,7 @@
       <c r="V3" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="W3" s="44" t="n">
+      <c r="W3" s="45" t="n">
         <v>19</v>
       </c>
       <c r="X3" s="2" t="n">
@@ -33114,7 +32872,7 @@
           <t>2026.03</t>
         </is>
       </c>
-      <c r="W4" s="45" t="inlineStr">
+      <c r="W4" s="46" t="inlineStr">
         <is>
           <t>2026.06</t>
         </is>
@@ -33253,7 +33011,7 @@
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W5" s="46">
+      <c r="W5" s="47">
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33381,7 +33139,7 @@
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W6" s="46">
+      <c r="W6" s="47">
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33509,7 +33267,7 @@
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W7" s="46">
+      <c r="W7" s="47">
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33637,7 +33395,7 @@
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W8" s="46">
+      <c r="W8" s="47">
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33765,7 +33523,7 @@
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W9" s="46">
+      <c r="W9" s="47">
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33893,7 +33651,7 @@
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W10" s="47">
+      <c r="W10" s="48">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34021,7 +33779,7 @@
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W11" s="46">
+      <c r="W11" s="47">
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34149,7 +33907,7 @@
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W12" s="46">
+      <c r="W12" s="47">
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34277,7 +34035,7 @@
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W13" s="46">
+      <c r="W13" s="47">
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34405,7 +34163,7 @@
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W14" s="46">
+      <c r="W14" s="47">
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34533,7 +34291,7 @@
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W15" s="46">
+      <c r="W15" s="47">
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34661,7 +34419,7 @@
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W16" s="46">
+      <c r="W16" s="47">
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34789,7 +34547,7 @@
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W17" s="46">
+      <c r="W17" s="47">
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34917,7 +34675,7 @@
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W18" s="46">
+      <c r="W18" s="47">
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35045,7 +34803,7 @@
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W19" s="46">
+      <c r="W19" s="47">
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35173,7 +34931,7 @@
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W20" s="46">
+      <c r="W20" s="47">
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35301,7 +35059,7 @@
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W21" s="46">
+      <c r="W21" s="47">
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35429,7 +35187,7 @@
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W22" s="46">
+      <c r="W22" s="47">
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35557,7 +35315,7 @@
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W23" s="46">
+      <c r="W23" s="47">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35685,7 +35443,7 @@
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W24" s="46">
+      <c r="W24" s="47">
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35813,7 +35571,7 @@
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W25" s="46">
+      <c r="W25" s="47">
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35941,7 +35699,7 @@
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W26" s="46">
+      <c r="W26" s="47">
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36069,7 +35827,7 @@
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W27" s="46">
+      <c r="W27" s="47">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36197,7 +35955,7 @@
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W28" s="46">
+      <c r="W28" s="47">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36325,7 +36083,7 @@
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W29" s="46">
+      <c r="W29" s="47">
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36453,7 +36211,7 @@
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W30" s="46">
+      <c r="W30" s="47">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36581,7 +36339,7 @@
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W31" s="46">
+      <c r="W31" s="47">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36709,7 +36467,7 @@
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W32" s="46">
+      <c r="W32" s="47">
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36837,7 +36595,7 @@
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W33" s="48">
+      <c r="W33" s="49">
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36965,7 +36723,7 @@
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W34" s="46">
+      <c r="W34" s="47">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37093,7 +36851,7 @@
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W35" s="46">
+      <c r="W35" s="47">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37221,7 +36979,7 @@
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W36" s="46">
+      <c r="W36" s="47">
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37349,7 +37107,7 @@
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W37" s="46">
+      <c r="W37" s="47">
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37477,47 +37235,47 @@
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W38" s="49">
+      <c r="W38" s="50">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="X38" s="40">
+      <c r="X38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(X$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y38" s="40">
+      <c r="Y38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(Y$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z38" s="40">
+      <c r="Z38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(Z$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA38" s="40">
+      <c r="AA38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AA$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB38" s="40">
+      <c r="AB38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AB$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC38" s="40">
+      <c r="AC38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AC$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD38" s="40">
+      <c r="AD38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AD$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE38" s="40">
+      <c r="AE38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AE$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF38" s="40">
+      <c r="AF38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AF$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG38" s="40">
+      <c r="AG38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AG$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37605,47 +37363,47 @@
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W39" s="49">
+      <c r="W39" s="50">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="X39" s="40">
+      <c r="X39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(X$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y39" s="40">
+      <c r="Y39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(Y$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z39" s="40">
+      <c r="Z39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(Z$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA39" s="40">
+      <c r="AA39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AA$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB39" s="40">
+      <c r="AB39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AB$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC39" s="40">
+      <c r="AC39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AC$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD39" s="40">
+      <c r="AD39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AD$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE39" s="40">
+      <c r="AE39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AE$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF39" s="40">
+      <c r="AF39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AF$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG39" s="40">
+      <c r="AG39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AG$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37733,7 +37491,7 @@
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W40" s="46">
+      <c r="W40" s="47">
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37861,7 +37619,7 @@
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W41" s="46">
+      <c r="W41" s="47">
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37989,7 +37747,7 @@
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W42" s="47">
+      <c r="W42" s="48">
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38101,7 +37859,7 @@
         <f>IFERROR(V5/R5-1,"")</f>
         <v/>
       </c>
-      <c r="W43" s="47">
+      <c r="W43" s="48">
         <f>IFERROR(W5/S5-1,"")</f>
         <v/>
       </c>
@@ -38213,7 +37971,7 @@
         <f>IFERROR(V9/R9-1,"")</f>
         <v/>
       </c>
-      <c r="W44" s="47">
+      <c r="W44" s="48">
         <f>IFERROR(W9/S9-1,"")</f>
         <v/>
       </c>
@@ -38325,7 +38083,7 @@
         <f>IFERROR(V21/R21-1,"")</f>
         <v/>
       </c>
-      <c r="W45" s="47">
+      <c r="W45" s="48">
         <f>IFERROR(W21/S21-1,"")</f>
         <v/>
       </c>
@@ -38416,7 +38174,7 @@
       <c r="H1" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="I1" s="42" t="n">
+      <c r="I1" s="43" t="n">
         <v>2025</v>
       </c>
       <c r="J1" s="3" t="n">
@@ -38436,10 +38194,10 @@
         </is>
       </c>
       <c r="D2" s="18">
-        <f>변수!D46</f>
-        <v/>
-      </c>
-      <c r="I2" s="43" t="n"/>
+        <f>변수!D45</f>
+        <v/>
+      </c>
+      <c r="I2" s="44" t="n"/>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -38464,7 +38222,7 @@
       <c r="H3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="44" t="n">
+      <c r="I3" s="45" t="n">
         <v>5</v>
       </c>
       <c r="J3" s="2" t="n">
@@ -38498,7 +38256,7 @@
           <t>2024.12A</t>
         </is>
       </c>
-      <c r="I4" s="45" t="inlineStr">
+      <c r="I4" s="46" t="inlineStr">
         <is>
           <t>2025.12A</t>
         </is>
@@ -38546,7 +38304,7 @@
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="47">
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38590,7 +38348,7 @@
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I6" s="46">
+      <c r="I6" s="47">
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38634,7 +38392,7 @@
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I7" s="46">
+      <c r="I7" s="47">
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38678,7 +38436,7 @@
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I8" s="46">
+      <c r="I8" s="47">
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38722,7 +38480,7 @@
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I9" s="46">
+      <c r="I9" s="47">
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38766,7 +38524,7 @@
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I10" s="47">
+      <c r="I10" s="48">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38810,7 +38568,7 @@
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="47">
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38854,7 +38612,7 @@
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I12" s="46">
+      <c r="I12" s="47">
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38898,7 +38656,7 @@
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I13" s="46">
+      <c r="I13" s="47">
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38942,7 +38700,7 @@
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="47">
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38986,7 +38744,7 @@
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I15" s="46">
+      <c r="I15" s="47">
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39030,7 +38788,7 @@
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="47">
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39074,7 +38832,7 @@
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I17" s="46">
+      <c r="I17" s="47">
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39118,7 +38876,7 @@
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I18" s="46">
+      <c r="I18" s="47">
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39162,7 +38920,7 @@
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="47">
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39206,7 +38964,7 @@
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I20" s="46">
+      <c r="I20" s="47">
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39250,7 +39008,7 @@
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I21" s="46">
+      <c r="I21" s="47">
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39294,7 +39052,7 @@
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I22" s="46">
+      <c r="I22" s="47">
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39338,7 +39096,7 @@
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I23" s="46">
+      <c r="I23" s="47">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39382,7 +39140,7 @@
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I24" s="46">
+      <c r="I24" s="47">
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39426,7 +39184,7 @@
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="47">
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39470,7 +39228,7 @@
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I26" s="46">
+      <c r="I26" s="47">
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39514,7 +39272,7 @@
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I27" s="46">
+      <c r="I27" s="47">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39558,7 +39316,7 @@
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I28" s="46">
+      <c r="I28" s="47">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39602,7 +39360,7 @@
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I29" s="46">
+      <c r="I29" s="47">
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39646,7 +39404,7 @@
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I30" s="46">
+      <c r="I30" s="47">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39690,7 +39448,7 @@
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I31" s="46">
+      <c r="I31" s="47">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39734,7 +39492,7 @@
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I32" s="46">
+      <c r="I32" s="47">
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39778,7 +39536,7 @@
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I33" s="48">
+      <c r="I33" s="49">
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39822,7 +39580,7 @@
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I34" s="46">
+      <c r="I34" s="47">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39866,7 +39624,7 @@
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I35" s="46">
+      <c r="I35" s="47">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39910,7 +39668,7 @@
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I36" s="46">
+      <c r="I36" s="47">
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39954,7 +39712,7 @@
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I37" s="46">
+      <c r="I37" s="47">
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39998,19 +39756,19 @@
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I38" s="49">
+      <c r="I38" s="50">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J38" s="40">
+      <c r="J38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K38" s="40">
+      <c r="K38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L38" s="40">
+      <c r="L38" s="41">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -40042,19 +39800,19 @@
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I39" s="49">
+      <c r="I39" s="50">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J39" s="40">
+      <c r="J39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K39" s="40">
+      <c r="K39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L39" s="40">
+      <c r="L39" s="41">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -40086,7 +39844,7 @@
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I40" s="46">
+      <c r="I40" s="47">
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -40130,7 +39888,7 @@
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I41" s="46">
+      <c r="I41" s="47">
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -40174,7 +39932,7 @@
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I42" s="47">
+      <c r="I42" s="48">
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -40214,7 +39972,7 @@
         <f>IFERROR(H5/G5-1,"")</f>
         <v/>
       </c>
-      <c r="I43" s="47">
+      <c r="I43" s="48">
         <f>IFERROR(I5/H5-1,"")</f>
         <v/>
       </c>
@@ -40254,7 +40012,7 @@
         <f>IFERROR(H9/G9-1,"")</f>
         <v/>
       </c>
-      <c r="I44" s="47">
+      <c r="I44" s="48">
         <f>IFERROR(I9/H9-1,"")</f>
         <v/>
       </c>
@@ -40294,7 +40052,7 @@
         <f>IFERROR(H21/G21-1,"")</f>
         <v/>
       </c>
-      <c r="I45" s="47">
+      <c r="I45" s="48">
         <f>IFERROR(I21/H21-1,"")</f>
         <v/>
       </c>
@@ -40335,7 +40093,7 @@
         </is>
       </c>
       <c r="C1" s="18">
-        <f>변수!D46</f>
+        <f>변수!D45</f>
         <v/>
       </c>
     </row>
@@ -40346,7 +40104,7 @@
         </is>
       </c>
       <c r="C2">
-        <f>변수!D47</f>
+        <f>변수!D46</f>
         <v/>
       </c>
     </row>
@@ -40363,16 +40121,16 @@
           <t>FY</t>
         </is>
       </c>
-      <c r="D5" s="50" t="n">
+      <c r="D5" s="51" t="n">
         <v>2025</v>
       </c>
-      <c r="E5" s="50" t="n">
+      <c r="E5" s="51" t="n">
         <v>2026</v>
       </c>
-      <c r="F5" s="50" t="n">
+      <c r="F5" s="51" t="n">
         <v>2027</v>
       </c>
-      <c r="G5" s="50" t="n">
+      <c r="G5" s="51" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -40523,7 +40281,7 @@
         </is>
       </c>
       <c r="D14" s="18">
-        <f>IFERROR(E7*변수!D52+F7*(1-변수!D52),"")</f>
+        <f>IFERROR(E7*변수!D51+F7*(1-변수!D51),"")</f>
         <v/>
       </c>
     </row>
@@ -40534,7 +40292,7 @@
         </is>
       </c>
       <c r="D15" s="27">
-        <f>변수!D49</f>
+        <f>변수!D48</f>
         <v/>
       </c>
       <c r="E15" s="18">
@@ -40558,7 +40316,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D50</f>
+        <f>변수!D49</f>
         <v/>
       </c>
       <c r="E16" s="18">
@@ -40582,7 +40340,7 @@
         </is>
       </c>
       <c r="D17" s="27">
-        <f>변수!D51</f>
+        <f>변수!D50</f>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -40646,7 +40404,7 @@
         </is>
       </c>
       <c r="D23" s="21">
-        <f>변수!D48</f>
+        <f>변수!D47</f>
         <v/>
       </c>
     </row>
@@ -40701,7 +40459,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-271.4</v>
+        <v>-1083.5</v>
       </c>
     </row>
     <row r="30">
@@ -40711,7 +40469,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1124.9</v>
+        <v>4499.7</v>
       </c>
     </row>
     <row r="31">
@@ -40728,7 +40486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.27</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="33">
@@ -40738,7 +40496,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.2413</v>
+        <v>-0.2408</v>
       </c>
     </row>
     <row r="34">
@@ -41293,43 +41051,43 @@
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X5" s="40">
+      <c r="X5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y5" s="40">
+      <c r="Y5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z5" s="40">
+      <c r="Z5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA5" s="40">
+      <c r="AA5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB5" s="40">
+      <c r="AB5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC5" s="40">
+      <c r="AC5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD5" s="40">
+      <c r="AD5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE5" s="40">
+      <c r="AE5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF5" s="40">
+      <c r="AF5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG5" s="40">
+      <c r="AG5" s="41">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -41535,43 +41293,43 @@
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X7" s="40">
+      <c r="X7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y7" s="40">
+      <c r="Y7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z7" s="40">
+      <c r="Z7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA7" s="40">
+      <c r="AA7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB7" s="40">
+      <c r="AB7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC7" s="40">
+      <c r="AC7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD7" s="40">
+      <c r="AD7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE7" s="40">
+      <c r="AE7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF7" s="40">
+      <c r="AF7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG7" s="40">
+      <c r="AG7" s="41">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -41777,43 +41535,43 @@
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X9" s="40">
+      <c r="X9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y9" s="40">
+      <c r="Y9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z9" s="40">
+      <c r="Z9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA9" s="40">
+      <c r="AA9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB9" s="40">
+      <c r="AB9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC9" s="40">
+      <c r="AC9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD9" s="40">
+      <c r="AD9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE9" s="40">
+      <c r="AE9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF9" s="40">
+      <c r="AF9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG9" s="40">
+      <c r="AG9" s="41">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -42019,43 +41777,43 @@
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X11" s="40">
+      <c r="X11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y11" s="40">
+      <c r="Y11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z11" s="40">
+      <c r="Z11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA11" s="40">
+      <c r="AA11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB11" s="40">
+      <c r="AB11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC11" s="40">
+      <c r="AC11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD11" s="40">
+      <c r="AD11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE11" s="40">
+      <c r="AE11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF11" s="40">
+      <c r="AF11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG11" s="40">
+      <c r="AG11" s="41">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -42261,43 +42019,43 @@
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X13" s="40">
+      <c r="X13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y13" s="40">
+      <c r="Y13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z13" s="40">
+      <c r="Z13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA13" s="40">
+      <c r="AA13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB13" s="40">
+      <c r="AB13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC13" s="40">
+      <c r="AC13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD13" s="40">
+      <c r="AD13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE13" s="40">
+      <c r="AE13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF13" s="40">
+      <c r="AF13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG13" s="40">
+      <c r="AG13" s="41">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -42445,7 +42203,7 @@
         </is>
       </c>
       <c r="D16" s="27">
-        <f>변수!D59</f>
+        <f>변수!D58</f>
         <v/>
       </c>
       <c r="E16" s="2" t="inlineStr">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5274,35 +5274,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5393,35 +5393,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5512,35 +5512,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5631,35 +5631,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5750,35 +5750,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5869,35 +5869,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5988,35 +5988,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6107,35 +6107,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -9681,7 +9681,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,518원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,586원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="D53" s="36" t="n">
-        <v>0.2495927601809955</v>
+        <v>0.2495927601809954</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.008530302041496976</v>
+        <v>0.008530302041496889</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4396,7 +4396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5274,35 +5274,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5393,35 +5393,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5512,35 +5512,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5631,35 +5631,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5750,35 +5750,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5869,35 +5869,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5988,35 +5988,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6107,35 +6107,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4396,7 +4396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4396,7 +4396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
         <v>1443</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1427</v>
+        <v>1418</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6515,7 +6515,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1509.8</v>
+        <v>1494.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9677,7 +9677,7 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>1427</v>
+        <v>1418</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4396,7 +4396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5274,35 +5274,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5393,35 +5393,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5512,35 +5512,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5631,35 +5631,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5750,35 +5750,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5869,35 +5869,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5988,35 +5988,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6107,35 +6107,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6242,7 +6242,7 @@
         <v>1443</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1418</v>
+        <v>1314</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6424,7 +6424,7 @@
         <v>680</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1331</v>
+        <v>1314</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6515,7 +6515,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1494.5</v>
+        <v>1468.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9677,11 +9677,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>1418</v>
+        <v>1314</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,586원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,427원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40486,7 +40486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4396,7 +4396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5274,35 +5274,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5393,35 +5393,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5512,35 +5512,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5631,35 +5631,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5750,35 +5750,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5869,35 +5869,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5988,35 +5988,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6107,35 +6107,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6242,7 +6242,7 @@
         <v>1443</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6424,7 +6424,7 @@
         <v>680</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1314</v>
+        <v>1269</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6515,7 +6515,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1468.7</v>
+        <v>1448.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9677,11 +9677,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,427원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,418원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -4396,7 +4396,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5274,35 +5274,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5393,35 +5393,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5512,35 +5512,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5631,35 +5631,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5750,35 +5750,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5869,35 +5869,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5988,35 +5988,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6107,35 +6107,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6242,7 +6242,7 @@
         <v>1443</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1310</v>
+        <v>1101</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6424,7 +6424,7 @@
         <v>680</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1269</v>
+        <v>1083</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6515,7 +6515,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1448.9</v>
+        <v>1371.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9677,11 +9677,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>1310</v>
+        <v>1101</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,418원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,206원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18643,7 +18643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38207,7 +38207,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -40486,7 +40486,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/101000_model.xlsx
+++ b/argus/kship/models/101000_model.xlsx
@@ -119,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,7 +167,6 @@
     <xf numFmtId="10" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1679,61 +1678,61 @@
     <comment ref="AC41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AF41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AG41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AH41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AI41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AN41" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전분기 − 1
-유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4</t>
+유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979</t>
       </text>
     </comment>
     <comment ref="AD42" authorId="0" shapeId="0">
@@ -3331,156 +3330,156 @@
     </comment>
     <comment ref="E33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/4(환산 — 2023Q1 1/4 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="G33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/4(환산 — 2023Q1 1/4 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="H33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/4(환산 — 2023Q1 1/4 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="I33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/4(환산 — 2023Q1 1/4 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="J33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/16(환산 — 2023Q1 1/4 병합 · 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 71,750,792주 × 1/4(환산 — 2023Q1 1/4 병합; IAS 33.64 비교표시·수정주가 이력과 정합)</t>
       </text>
     </comment>
     <comment ref="L33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 17,937,698주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="M33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 18,779,448주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="N33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 18,779,448주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="O33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 18,779,448주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="Q33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 22,842,424주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="R33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 30,132,955주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="S33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 30,132,640주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="T33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 30,630,152주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="V33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,254,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="W33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,429,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="X33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,429,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="Y33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 33,429,823주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="AA33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 39,624,969주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="AB33" authorId="0" shapeId="0">
       <text>
-        <t>추정(실적 구간 갭필): fin.shares.common_outstanding 39,624,969주 × 1/4(환산 — 2026Q2 분기말 후 1/4(aik 상장주식수); IAS 33.64 비교표시·수정주가 이력과 정합)</t>
+        <t>실측(계정 매핑 없음(파생·부문·시세 행) — 모델값 직접) — fin.shares.common_outstanding</t>
       </text>
     </comment>
     <comment ref="AC33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AD33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AF33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AG33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AH33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AI33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AK33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AL33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AM33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
     <comment ref="AN33" authorId="0" shapeId="0">
       <text>
-        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 — 분기말 후 병합) − 자기주식 16,979 × 1/4
+        <t>추정: 유통주식수 유지 — prices.json shares_outstanding(aik 상장 14,796,480 vs fin 2026Q2 보통주 발행 39,641,948, 비율 0.3733 비정수 감소 — 병합/소각 미확인) − 자기주식 16,979
 [qoq]</t>
       </text>
     </comment>
@@ -3546,7 +3545,7 @@
     </comment>
     <comment ref="AB35" authorId="0" shapeId="0">
       <text>
-        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 36억 × (1 − 세율 0.2% [분기 유효세율(법인세 0억 ÷ 세전 25억)]) × 지배 비중 1.0000 [그 분기 지배NI/NI] = -10억 ÷ 유통주식수 · 초과 = 비영업손익 33억 − 12분기 기준선 -2억 · 보고 EPS 254원(EPS 행 불변) · 상수 35.56·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
+        <t>조정EPS 산식(모델 추정, 일회성 여부·세효과 주석 미확인): 지배NI − 초과 비영업손익 36억 × (1 − 세율 0.2% [분기 유효세율(법인세 0억 ÷ 세전 25억)]) × 지배 비중 1.0000 [그 분기 지배NI/NI] = -10억 ÷ 유통주식수 · 초과 = 비영업손익 33억 − 12분기 기준선 -2억 · 보고 EPS 64원(EPS 행 불변) · 상수 35.56·1.0 는 모델 one_offs_detected 값(세전·법인세 셀을 바꿔도 재계산되지 않음)</t>
       </text>
     </comment>
     <comment ref="AC35" authorId="0" shapeId="0">
@@ -4396,7 +4395,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4558,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>· 조정EPS(일회성 의심 1분기: 2026Q2 보고 254→조정 -105원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
+          <t>· 조정EPS(일회성 의심 1분기: 2026Q2 보고 64→조정 -26원) — 의심 분기 = 지배NI − (비영업손익 − 12분기 기준선) × (1 − 세율) × 지배 비중 ÷ 유통주식수(subQ 수식+메모, 세후 초과·지배 비중은 모델 상수), 다른 분기 = EPS. 보고 EPS 행·TP 12M fwd EPS(추정 분기만) 는 불변. 일회성 여부·세효과는 주석 미확인(모델 추정)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4603,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.45 가 단일 검정 5% 임계 r 0.71 미달(n=8, n_eff=8) (suppliers_mentions·시차 3·수준·창 8)): 전년동기 × (1+g) 추세 / 분기말 후 병합: aik 상장주식수 9,910,487 = fin 2026Q2 보통주 발행 39,641,948 × 1/4 → 최신 유통주식수 9,906,242(자기주식 16,979 × 1/4 차감) — 실적 분기 주식수·EPS·BPS·DPS 를 1/4 로 환산(IAS 33.64 비교표시·수정주가 이력과 정합), 추정 분기·PER/PBR now·EV 는 최신 주식수. 효력일·단수주 처리는 정기보고서 캐시 밖(주요사항보고서 미수집) / 주식수 사건 환산: 2023Q1 1/4 병합(eps_reported 교차검증 confirmed) → 사건 전 실적 19분기의 주식수·EPS·BPS·DPS 를 비율 환산(IAS 33.64; 셀 kind estimate, basis 에 원주식수·비율) / 이자발생자산 이자율: 주석 연율 2.8% 이상(주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la)) → CF 연율 0.9% 로 클립(assumptions.interest_rate_check) / 총차입금 이자율: 주석 연율 16.0% 이상(주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 2.75배 · CF 창 2022Q4~2024Q1(la −9분기) 가 주석 창(~2026Q1)보다 오래됨 → CF 로 교체 안 함) — 더 오래된 CF 연율 5.8% 로 바꾸지 않고 주석 유지(assumptions.interest_rate_check) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 33억(영업이익 -8억의 4배, 12분기 중위 4억·기준선 -2억) → 지배NI 25억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -104.7원(보고 254.2원; 초과 비영업손익 36억 × (1 − 세율 0.2%) × 지배 비중 1.00 = 36억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -2/+5/-3/+41(중위 +2억) → 추정 2026Q3 -7억(차 -9억, -590%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
+          <t>한계: 모델 quality.warnings — 매출 드라이버 폴백(고객 연동 격자 상관 0.45 가 단일 검정 5% 임계 r 0.71 미달(n=8, n_eff=8) (suppliers_mentions·시차 3·수준·창 8)): 전년동기 × (1+g) 추세 / 분기말 후 주식수 감소 비정수: aik 상장주식수 14,796,480 / fin 2026Q2 보통주 발행 39,641,948 = 0.3733 — 병합+소각 복합 가능 → SHARE_EVENTS 수동 확인; 최신 주식수만 14,779,501 로 바꾸고 실적은 환산하지 않음 / 주식수 사건 환산: 2023Q1 1/4 병합(eps_reported 교차검증 confirmed) → 사건 전 실적 5분기의 주식수·EPS·BPS·DPS 를 비율 환산(IAS 33.64; 셀 kind estimate, basis 에 원주식수·비율) / 이자발생자산 이자율: 주석 연율 2.8% 이상(주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 3.24배 · CF 창 2025Q3~2026Q2(= la)) → CF 연율 0.9% 로 클립(assumptions.interest_rate_check) / 총차입금 이자율: 주석 연율 16.0% 이상(주석 마지막 분기 2026Q1 ≠ 마지막 실적 2026Q2(stale) · 주석/CF 2.75배 · CF 창 2022Q4~2024Q1(la −9분기) 가 주석 창(~2026Q1)보다 오래됨 → CF 로 교체 안 함) — 더 오래된 CF 연율 5.8% 로 바꾸지 않고 주석 유지(assumptions.interest_rate_check) / 감가상각비가 face·CF 에 없음(주석 미파싱) → EBITDA·EV/EBITDA 미산출 / 일회성 의심 2026Q2: 비영업손익 33억(영업이익 -8억의 4배, 12분기 중위 4억·기준선 -2억) → 지배NI 25억·보고 EPS·FY2026 합계·TTM PER 에 그대로 포함 — 처분이익 등 일회성 여부는 주석 확인 전까지 미확정(12M fwd EPS 에는 미포함) · 조정EPS -26.2원(보고 63.6원; 초과 비영업손익 36억 × (1 − 세율 0.2%) × 지배 비중 1.00 = 36억 차감 — 추정, 조정EPS 행) / 금융손익 실적→추정 단절: 최근 4분기 실적 -2/+5/-3/+41(중위 +2억) → 추정 2026Q3 -7억(차 -9억, -590%) — 추정은 이자손익 + 기타금융 중위, 외환·파생 평가손익 0 가정(환율 효과는 환관련손익 행). 값은 바꾸지 않음 — 지배NI·EPS 해석 시 참고</t>
         </is>
       </c>
     </row>
@@ -5274,35 +5273,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5393,35 +5392,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5512,35 +5511,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5631,35 +5630,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5750,35 +5749,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5869,35 +5868,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -5988,35 +5987,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6107,35 +6106,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6242,7 +6241,7 @@
         <v>1443</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>1101</v>
+        <v>986</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6424,7 +6423,7 @@
         <v>680</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>1083</v>
+        <v>815</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6515,7 +6514,7 @@
         <v>1132.7</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>1371.8</v>
+        <v>1265.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9439,7 +9438,7 @@
         <v/>
       </c>
       <c r="AC41" s="24" t="n">
-        <v>-2.5e-08</v>
+        <v>-0.627015748</v>
       </c>
       <c r="AD41" s="24" t="n">
         <v>0</v>
@@ -9677,11 +9676,11 @@
         </is>
       </c>
       <c r="D45" s="34" t="n">
-        <v>1101</v>
+        <v>986</v>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,206원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 1,000원)</t>
         </is>
       </c>
       <c r="F45" s="9" t="n"/>
@@ -9717,7 +9716,7 @@
       </c>
       <c r="D46" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -10543,7 +10542,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -18643,7 +18642,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -30658,81 +30657,81 @@
         </is>
       </c>
       <c r="E33" s="32" t="n">
-        <v>4.4844245</v>
+        <v>17.937698</v>
       </c>
       <c r="F33" s="28">
         <f>E33</f>
         <v/>
       </c>
       <c r="G33" s="32" t="n">
-        <v>4.4844245</v>
+        <v>17.937698</v>
       </c>
       <c r="H33" s="32" t="n">
-        <v>4.4844245</v>
+        <v>17.937698</v>
       </c>
       <c r="I33" s="32" t="n">
-        <v>4.4844245</v>
+        <v>17.937698</v>
       </c>
       <c r="J33" s="32" t="n">
-        <v>4.4844245</v>
+        <v>17.937698</v>
       </c>
       <c r="K33" s="28">
         <f>J33</f>
         <v/>
       </c>
-      <c r="L33" s="32" t="n">
-        <v>4.4844245</v>
-      </c>
-      <c r="M33" s="32" t="n">
-        <v>4.694862</v>
-      </c>
-      <c r="N33" s="32" t="n">
-        <v>4.694862</v>
-      </c>
-      <c r="O33" s="32" t="n">
-        <v>4.694862</v>
+      <c r="L33" s="27" t="n">
+        <v>17.938</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>18.779</v>
+      </c>
+      <c r="N33" s="27" t="n">
+        <v>18.779</v>
+      </c>
+      <c r="O33" s="27" t="n">
+        <v>18.779</v>
       </c>
       <c r="P33" s="28">
         <f>O33</f>
         <v/>
       </c>
-      <c r="Q33" s="32" t="n">
-        <v>5.710606</v>
-      </c>
-      <c r="R33" s="32" t="n">
-        <v>7.53323875</v>
-      </c>
-      <c r="S33" s="32" t="n">
-        <v>7.53316</v>
-      </c>
-      <c r="T33" s="32" t="n">
-        <v>7.657538</v>
+      <c r="Q33" s="27" t="n">
+        <v>22.842</v>
+      </c>
+      <c r="R33" s="27" t="n">
+        <v>30.133</v>
+      </c>
+      <c r="S33" s="27" t="n">
+        <v>30.133</v>
+      </c>
+      <c r="T33" s="27" t="n">
+        <v>30.63</v>
       </c>
       <c r="U33" s="28">
         <f>T33</f>
         <v/>
       </c>
-      <c r="V33" s="32" t="n">
-        <v>8.31370575</v>
-      </c>
-      <c r="W33" s="32" t="n">
-        <v>8.35745575</v>
-      </c>
-      <c r="X33" s="32" t="n">
-        <v>8.35745575</v>
-      </c>
-      <c r="Y33" s="32" t="n">
-        <v>8.35745575</v>
+      <c r="V33" s="27" t="n">
+        <v>33.255</v>
+      </c>
+      <c r="W33" s="27" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="X33" s="27" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="Y33" s="27" t="n">
+        <v>33.43</v>
       </c>
       <c r="Z33" s="28">
         <f>Y33</f>
         <v/>
       </c>
-      <c r="AA33" s="32" t="n">
-        <v>9.90624225</v>
-      </c>
-      <c r="AB33" s="39" t="n">
-        <v>9.90624225</v>
+      <c r="AA33" s="27" t="n">
+        <v>39.625</v>
+      </c>
+      <c r="AB33" s="29" t="n">
+        <v>39.625</v>
       </c>
       <c r="AC33" s="32">
         <f>IFERROR(AB33*(1+변수!AC41),"")</f>
@@ -31064,7 +31063,7 @@
         <f>IFERROR(AA34,"")</f>
         <v/>
       </c>
-      <c r="AB35" s="40">
+      <c r="AB35" s="39">
         <f>IFERROR((AB21-(35.56)*(1.0))*100/AB33,"")</f>
         <v/>
       </c>
@@ -31458,25 +31457,25 @@
       </c>
       <c r="AA38" s="13" t="n"/>
       <c r="AB38" s="15" t="n"/>
-      <c r="AC38" s="41" t="n"/>
-      <c r="AD38" s="41" t="n"/>
-      <c r="AE38" s="42">
+      <c r="AC38" s="40" t="n"/>
+      <c r="AD38" s="40" t="n"/>
+      <c r="AE38" s="41">
         <f>AD38</f>
         <v/>
       </c>
-      <c r="AF38" s="41" t="n"/>
-      <c r="AG38" s="41" t="n"/>
-      <c r="AH38" s="41" t="n"/>
-      <c r="AI38" s="41" t="n"/>
-      <c r="AJ38" s="42">
+      <c r="AF38" s="40" t="n"/>
+      <c r="AG38" s="40" t="n"/>
+      <c r="AH38" s="40" t="n"/>
+      <c r="AI38" s="40" t="n"/>
+      <c r="AJ38" s="41">
         <f>AI38</f>
         <v/>
       </c>
-      <c r="AK38" s="41" t="n"/>
-      <c r="AL38" s="41" t="n"/>
-      <c r="AM38" s="41" t="n"/>
-      <c r="AN38" s="41" t="n"/>
-      <c r="AO38" s="42">
+      <c r="AK38" s="40" t="n"/>
+      <c r="AL38" s="40" t="n"/>
+      <c r="AM38" s="40" t="n"/>
+      <c r="AN38" s="40" t="n"/>
+      <c r="AO38" s="41">
         <f>AN38</f>
         <v/>
       </c>
@@ -31598,55 +31597,55 @@
         <f>IFERROR(변수!AB18/AB36,"")</f>
         <v/>
       </c>
-      <c r="AC39" s="41">
+      <c r="AC39" s="40">
         <f>IFERROR(변수!$D$45/AC36,"")</f>
         <v/>
       </c>
-      <c r="AD39" s="41">
+      <c r="AD39" s="40">
         <f>IFERROR(변수!$D$45/AD36,"")</f>
         <v/>
       </c>
-      <c r="AE39" s="42">
+      <c r="AE39" s="41">
         <f>AD39</f>
         <v/>
       </c>
-      <c r="AF39" s="41">
+      <c r="AF39" s="40">
         <f>IFERROR(변수!$D$45/AF36,"")</f>
         <v/>
       </c>
-      <c r="AG39" s="41">
+      <c r="AG39" s="40">
         <f>IFERROR(변수!$D$45/AG36,"")</f>
         <v/>
       </c>
-      <c r="AH39" s="41">
+      <c r="AH39" s="40">
         <f>IFERROR(변수!$D$45/AH36,"")</f>
         <v/>
       </c>
-      <c r="AI39" s="41">
+      <c r="AI39" s="40">
         <f>IFERROR(변수!$D$45/AI36,"")</f>
         <v/>
       </c>
-      <c r="AJ39" s="42">
+      <c r="AJ39" s="41">
         <f>AI39</f>
         <v/>
       </c>
-      <c r="AK39" s="41">
+      <c r="AK39" s="40">
         <f>IFERROR(변수!$D$45/AK36,"")</f>
         <v/>
       </c>
-      <c r="AL39" s="41">
+      <c r="AL39" s="40">
         <f>IFERROR(변수!$D$45/AL36,"")</f>
         <v/>
       </c>
-      <c r="AM39" s="41">
+      <c r="AM39" s="40">
         <f>IFERROR(변수!$D$45/AM36,"")</f>
         <v/>
       </c>
-      <c r="AN39" s="41">
+      <c r="AN39" s="40">
         <f>IFERROR(변수!$D$45/AN36,"")</f>
         <v/>
       </c>
-      <c r="AO39" s="42">
+      <c r="AO39" s="41">
         <f>AN39</f>
         <v/>
       </c>
@@ -32614,7 +32613,7 @@
           <t>1Q26</t>
         </is>
       </c>
-      <c r="W1" s="43" t="inlineStr">
+      <c r="W1" s="42" t="inlineStr">
         <is>
           <t>2Q26</t>
         </is>
@@ -32680,7 +32679,7 @@
         <f>변수!D45</f>
         <v/>
       </c>
-      <c r="W2" s="44" t="n"/>
+      <c r="W2" s="43" t="n"/>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -32690,7 +32689,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -32747,7 +32746,7 @@
       <c r="V3" s="2" t="n">
         <v>18</v>
       </c>
-      <c r="W3" s="45" t="n">
+      <c r="W3" s="44" t="n">
         <v>19</v>
       </c>
       <c r="X3" s="2" t="n">
@@ -32872,7 +32871,7 @@
           <t>2026.03</t>
         </is>
       </c>
-      <c r="W4" s="46" t="inlineStr">
+      <c r="W4" s="45" t="inlineStr">
         <is>
           <t>2026.06</t>
         </is>
@@ -33011,7 +33010,7 @@
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W5" s="47">
+      <c r="W5" s="46">
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33139,7 +33138,7 @@
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W6" s="47">
+      <c r="W6" s="46">
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33267,7 +33266,7 @@
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W7" s="47">
+      <c r="W7" s="46">
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33395,7 +33394,7 @@
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W8" s="47">
+      <c r="W8" s="46">
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33523,7 +33522,7 @@
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W9" s="47">
+      <c r="W9" s="46">
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33651,7 +33650,7 @@
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W10" s="48">
+      <c r="W10" s="47">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33779,7 +33778,7 @@
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W11" s="47">
+      <c r="W11" s="46">
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -33907,7 +33906,7 @@
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W12" s="47">
+      <c r="W12" s="46">
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34035,7 +34034,7 @@
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W13" s="47">
+      <c r="W13" s="46">
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34163,7 +34162,7 @@
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W14" s="47">
+      <c r="W14" s="46">
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34291,7 +34290,7 @@
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W15" s="47">
+      <c r="W15" s="46">
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34419,7 +34418,7 @@
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W16" s="47">
+      <c r="W16" s="46">
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34547,7 +34546,7 @@
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W17" s="47">
+      <c r="W17" s="46">
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34675,7 +34674,7 @@
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W18" s="47">
+      <c r="W18" s="46">
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34803,7 +34802,7 @@
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W19" s="47">
+      <c r="W19" s="46">
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -34931,7 +34930,7 @@
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W20" s="47">
+      <c r="W20" s="46">
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35059,7 +35058,7 @@
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W21" s="47">
+      <c r="W21" s="46">
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35187,7 +35186,7 @@
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W22" s="47">
+      <c r="W22" s="46">
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35315,7 +35314,7 @@
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W23" s="47">
+      <c r="W23" s="46">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35443,7 +35442,7 @@
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W24" s="47">
+      <c r="W24" s="46">
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35571,7 +35570,7 @@
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W25" s="47">
+      <c r="W25" s="46">
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35699,7 +35698,7 @@
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W26" s="47">
+      <c r="W26" s="46">
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35827,7 +35826,7 @@
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W27" s="47">
+      <c r="W27" s="46">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -35955,7 +35954,7 @@
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W28" s="47">
+      <c r="W28" s="46">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36083,7 +36082,7 @@
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W29" s="47">
+      <c r="W29" s="46">
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36211,7 +36210,7 @@
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W30" s="47">
+      <c r="W30" s="46">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36339,7 +36338,7 @@
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W31" s="47">
+      <c r="W31" s="46">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36467,7 +36466,7 @@
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W32" s="47">
+      <c r="W32" s="46">
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36595,7 +36594,7 @@
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W33" s="49">
+      <c r="W33" s="48">
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36723,7 +36722,7 @@
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W34" s="47">
+      <c r="W34" s="46">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36851,7 +36850,7 @@
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W35" s="47">
+      <c r="W35" s="46">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -36979,7 +36978,7 @@
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W36" s="47">
+      <c r="W36" s="46">
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37107,7 +37106,7 @@
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W37" s="47">
+      <c r="W37" s="46">
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37235,47 +37234,47 @@
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W38" s="50">
+      <c r="W38" s="49">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="X38" s="41">
+      <c r="X38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(X$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y38" s="41">
+      <c r="Y38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(Y$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z38" s="41">
+      <c r="Z38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(Z$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA38" s="41">
+      <c r="AA38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AA$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB38" s="41">
+      <c r="AB38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AB$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC38" s="41">
+      <c r="AC38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AC$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD38" s="41">
+      <c r="AD38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AD$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE38" s="41">
+      <c r="AE38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AE$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF38" s="41">
+      <c r="AF38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AF$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG38" s="41">
+      <c r="AG38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(AG$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37363,47 +37362,47 @@
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W39" s="50">
+      <c r="W39" s="49">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="X39" s="41">
+      <c r="X39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(X$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y39" s="41">
+      <c r="Y39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(Y$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z39" s="41">
+      <c r="Z39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(Z$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA39" s="41">
+      <c r="AA39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AA$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB39" s="41">
+      <c r="AB39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AB$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC39" s="41">
+      <c r="AC39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AC$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD39" s="41">
+      <c r="AD39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AD$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE39" s="41">
+      <c r="AE39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AE$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF39" s="41">
+      <c r="AF39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AF$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG39" s="41">
+      <c r="AG39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(AG$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37491,7 +37490,7 @@
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W40" s="47">
+      <c r="W40" s="46">
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37619,7 +37618,7 @@
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W41" s="47">
+      <c r="W41" s="46">
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37747,7 +37746,7 @@
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(V$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="W42" s="48">
+      <c r="W42" s="47">
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(W$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -37859,7 +37858,7 @@
         <f>IFERROR(V5/R5-1,"")</f>
         <v/>
       </c>
-      <c r="W43" s="48">
+      <c r="W43" s="47">
         <f>IFERROR(W5/S5-1,"")</f>
         <v/>
       </c>
@@ -37971,7 +37970,7 @@
         <f>IFERROR(V9/R9-1,"")</f>
         <v/>
       </c>
-      <c r="W44" s="48">
+      <c r="W44" s="47">
         <f>IFERROR(W9/S9-1,"")</f>
         <v/>
       </c>
@@ -38083,7 +38082,7 @@
         <f>IFERROR(V21/R21-1,"")</f>
         <v/>
       </c>
-      <c r="W45" s="48">
+      <c r="W45" s="47">
         <f>IFERROR(W21/S21-1,"")</f>
         <v/>
       </c>
@@ -38174,7 +38173,7 @@
       <c r="H1" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="I1" s="43" t="n">
+      <c r="I1" s="42" t="n">
         <v>2025</v>
       </c>
       <c r="J1" s="3" t="n">
@@ -38197,7 +38196,7 @@
         <f>변수!D45</f>
         <v/>
       </c>
-      <c r="I2" s="44" t="n"/>
+      <c r="I2" s="43" t="n"/>
     </row>
     <row r="3">
       <c r="C3" t="inlineStr">
@@ -38207,7 +38206,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -38222,7 +38221,7 @@
       <c r="H3" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="45" t="n">
+      <c r="I3" s="44" t="n">
         <v>5</v>
       </c>
       <c r="J3" s="2" t="n">
@@ -38256,7 +38255,7 @@
           <t>2024.12A</t>
         </is>
       </c>
-      <c r="I4" s="46" t="inlineStr">
+      <c r="I4" s="45" t="inlineStr">
         <is>
           <t>2025.12A</t>
         </is>
@@ -38304,7 +38303,7 @@
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="46">
         <f>IFERROR(VLOOKUP($A5,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38348,7 +38347,7 @@
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="46">
         <f>IFERROR(VLOOKUP($A6,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38392,7 +38391,7 @@
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="46">
         <f>IFERROR(VLOOKUP($A7,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38436,7 +38435,7 @@
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I8" s="47">
+      <c r="I8" s="46">
         <f>IFERROR(VLOOKUP($A8,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38480,7 +38479,7 @@
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="46">
         <f>IFERROR(VLOOKUP($A9,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38524,7 +38523,7 @@
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I10" s="48">
+      <c r="I10" s="47">
         <f>IFERROR(VLOOKUP($A10,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38568,7 +38567,7 @@
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="46">
         <f>IFERROR(VLOOKUP($A11,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38612,7 +38611,7 @@
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I12" s="47">
+      <c r="I12" s="46">
         <f>IFERROR(VLOOKUP($A12,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38656,7 +38655,7 @@
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I13" s="47">
+      <c r="I13" s="46">
         <f>IFERROR(VLOOKUP($A13,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38700,7 +38699,7 @@
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="46">
         <f>IFERROR(VLOOKUP($A14,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38744,7 +38743,7 @@
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I15" s="47">
+      <c r="I15" s="46">
         <f>IFERROR(VLOOKUP($A15,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38788,7 +38787,7 @@
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I16" s="47">
+      <c r="I16" s="46">
         <f>IFERROR(VLOOKUP($A16,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38832,7 +38831,7 @@
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="46">
         <f>IFERROR(VLOOKUP($A17,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38876,7 +38875,7 @@
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I18" s="47">
+      <c r="I18" s="46">
         <f>IFERROR(VLOOKUP($A18,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38920,7 +38919,7 @@
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I19" s="47">
+      <c r="I19" s="46">
         <f>IFERROR(VLOOKUP($A19,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -38964,7 +38963,7 @@
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I20" s="47">
+      <c r="I20" s="46">
         <f>IFERROR(VLOOKUP($A20,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39008,7 +39007,7 @@
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I21" s="47">
+      <c r="I21" s="46">
         <f>IFERROR(VLOOKUP($A21,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39052,7 +39051,7 @@
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I22" s="47">
+      <c r="I22" s="46">
         <f>IFERROR(VLOOKUP($A22,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39096,7 +39095,7 @@
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="46">
         <f>IFERROR(VLOOKUP($A23,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39140,7 +39139,7 @@
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I24" s="47">
+      <c r="I24" s="46">
         <f>IFERROR(VLOOKUP($A24,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39184,7 +39183,7 @@
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I25" s="47">
+      <c r="I25" s="46">
         <f>IFERROR(VLOOKUP($A25,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39228,7 +39227,7 @@
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I26" s="47">
+      <c r="I26" s="46">
         <f>IFERROR(VLOOKUP($A26,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39272,7 +39271,7 @@
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I27" s="47">
+      <c r="I27" s="46">
         <f>IFERROR(VLOOKUP($A27,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39316,7 +39315,7 @@
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I28" s="47">
+      <c r="I28" s="46">
         <f>IFERROR(VLOOKUP($A28,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39360,7 +39359,7 @@
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I29" s="47">
+      <c r="I29" s="46">
         <f>IFERROR(VLOOKUP($A29,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39404,7 +39403,7 @@
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I30" s="47">
+      <c r="I30" s="46">
         <f>IFERROR(VLOOKUP($A30,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39448,7 +39447,7 @@
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I31" s="47">
+      <c r="I31" s="46">
         <f>IFERROR(VLOOKUP($A31,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39492,7 +39491,7 @@
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I32" s="47">
+      <c r="I32" s="46">
         <f>IFERROR(VLOOKUP($A32,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39536,7 +39535,7 @@
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I33" s="49">
+      <c r="I33" s="48">
         <f>IFERROR(VLOOKUP($A33,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39580,7 +39579,7 @@
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I34" s="47">
+      <c r="I34" s="46">
         <f>IFERROR(VLOOKUP($A34,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39624,7 +39623,7 @@
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I35" s="47">
+      <c r="I35" s="46">
         <f>IFERROR(VLOOKUP($A35,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39668,7 +39667,7 @@
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I36" s="47">
+      <c r="I36" s="46">
         <f>IFERROR(VLOOKUP($A36,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39712,7 +39711,7 @@
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I37" s="47">
+      <c r="I37" s="46">
         <f>IFERROR(VLOOKUP($A37,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39756,19 +39755,19 @@
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I38" s="50">
+      <c r="I38" s="49">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J38" s="41">
+      <c r="J38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K38" s="41">
+      <c r="K38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L38" s="41">
+      <c r="L38" s="40">
         <f>IFERROR(VLOOKUP($A38,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39800,19 +39799,19 @@
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I39" s="50">
+      <c r="I39" s="49">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="J39" s="41">
+      <c r="J39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(J$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="K39" s="41">
+      <c r="K39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(K$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="L39" s="41">
+      <c r="L39" s="40">
         <f>IFERROR(VLOOKUP($A39,subQ,MATCH(L$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39844,7 +39843,7 @@
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I40" s="47">
+      <c r="I40" s="46">
         <f>IFERROR(VLOOKUP($A40,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39888,7 +39887,7 @@
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I41" s="47">
+      <c r="I41" s="46">
         <f>IFERROR(VLOOKUP($A41,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39932,7 +39931,7 @@
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(H$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
-      <c r="I42" s="48">
+      <c r="I42" s="47">
         <f>IFERROR(VLOOKUP($A42,subQ,MATCH(I$1,SUBQH,0),0),"")</f>
         <v/>
       </c>
@@ -39972,7 +39971,7 @@
         <f>IFERROR(H5/G5-1,"")</f>
         <v/>
       </c>
-      <c r="I43" s="48">
+      <c r="I43" s="47">
         <f>IFERROR(I5/H5-1,"")</f>
         <v/>
       </c>
@@ -40012,7 +40011,7 @@
         <f>IFERROR(H9/G9-1,"")</f>
         <v/>
       </c>
-      <c r="I44" s="48">
+      <c r="I44" s="47">
         <f>IFERROR(I9/H9-1,"")</f>
         <v/>
       </c>
@@ -40052,7 +40051,7 @@
         <f>IFERROR(H21/G21-1,"")</f>
         <v/>
       </c>
-      <c r="I45" s="48">
+      <c r="I45" s="47">
         <f>IFERROR(I21/H21-1,"")</f>
         <v/>
       </c>
@@ -40121,16 +40120,16 @@
           <t>FY</t>
         </is>
       </c>
-      <c r="D5" s="51" t="n">
+      <c r="D5" s="50" t="n">
         <v>2025</v>
       </c>
-      <c r="E5" s="51" t="n">
+      <c r="E5" s="50" t="n">
         <v>2026</v>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="50" t="n">
         <v>2027</v>
       </c>
-      <c r="G5" s="51" t="n">
+      <c r="G5" s="50" t="n">
         <v>2028</v>
       </c>
     </row>
@@ -40459,7 +40458,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-1083.5</v>
+        <v>-726.2</v>
       </c>
     </row>
     <row r="30">
@@ -40469,7 +40468,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4499.7</v>
+        <v>1124.9</v>
       </c>
     </row>
     <row r="31">
@@ -40486,7 +40485,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.24</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="33">
@@ -40496,7 +40495,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-0.2408</v>
+        <v>-0.6456</v>
       </c>
     </row>
     <row r="34">
@@ -41051,43 +41050,43 @@
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X5" s="41">
+      <c r="X5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y5" s="41">
+      <c r="Y5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z5" s="41">
+      <c r="Z5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA5" s="41">
+      <c r="AA5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB5" s="41">
+      <c r="AB5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC5" s="41">
+      <c r="AC5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD5" s="41">
+      <c r="AD5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE5" s="41">
+      <c r="AE5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF5" s="41">
+      <c r="AF5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG5" s="41">
+      <c r="AG5" s="40">
         <f>IFERROR(VLOOKUP($D5,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -41293,43 +41292,43 @@
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X7" s="41">
+      <c r="X7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y7" s="41">
+      <c r="Y7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z7" s="41">
+      <c r="Z7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA7" s="41">
+      <c r="AA7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB7" s="41">
+      <c r="AB7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC7" s="41">
+      <c r="AC7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD7" s="41">
+      <c r="AD7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE7" s="41">
+      <c r="AE7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF7" s="41">
+      <c r="AF7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG7" s="41">
+      <c r="AG7" s="40">
         <f>IFERROR(VLOOKUP($D7,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -41535,43 +41534,43 @@
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X9" s="41">
+      <c r="X9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y9" s="41">
+      <c r="Y9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z9" s="41">
+      <c r="Z9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA9" s="41">
+      <c r="AA9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB9" s="41">
+      <c r="AB9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC9" s="41">
+      <c r="AC9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD9" s="41">
+      <c r="AD9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE9" s="41">
+      <c r="AE9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF9" s="41">
+      <c r="AF9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG9" s="41">
+      <c r="AG9" s="40">
         <f>IFERROR(VLOOKUP($D9,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -41777,43 +41776,43 @@
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X11" s="41">
+      <c r="X11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y11" s="41">
+      <c r="Y11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z11" s="41">
+      <c r="Z11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA11" s="41">
+      <c r="AA11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB11" s="41">
+      <c r="AB11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC11" s="41">
+      <c r="AC11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD11" s="41">
+      <c r="AD11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE11" s="41">
+      <c r="AE11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF11" s="41">
+      <c r="AF11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG11" s="41">
+      <c r="AG11" s="40">
         <f>IFERROR(VLOOKUP($D11,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
@@ -42019,43 +42018,43 @@
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(W$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="X13" s="41">
+      <c r="X13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(X$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Y13" s="41">
+      <c r="Y13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(Y$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="Z13" s="41">
+      <c r="Z13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(Z$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AA13" s="41">
+      <c r="AA13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AA$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AB13" s="41">
+      <c r="AB13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AB$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AC13" s="41">
+      <c r="AC13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AC$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AD13" s="41">
+      <c r="AD13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AD$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AE13" s="41">
+      <c r="AE13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AE$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AF13" s="41">
+      <c r="AF13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AF$1,변수H,0),0),"")</f>
         <v/>
       </c>
-      <c r="AG13" s="41">
+      <c r="AG13" s="40">
         <f>IFERROR(VLOOKUP($D13,환율,MATCH(AG$1,변수H,0),0),"")</f>
         <v/>
       </c>
